--- a/research/traditional_assets/database/data/netherlands/netherlands_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_real_estate_general_diversified.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.08789999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="G2">
-        <v>-0.0265693190239618</v>
+        <v>-0.217289035328574</v>
       </c>
       <c r="H2">
-        <v>-0.0265693190239618</v>
+        <v>-0.217289035328574</v>
       </c>
       <c r="I2">
-        <v>-0.05704081612198328</v>
+        <v>-0.2044023430349625</v>
       </c>
       <c r="J2">
-        <v>-0.05704081612198328</v>
+        <v>-0.2044023430349625</v>
       </c>
       <c r="K2">
-        <v>-112.48</v>
+        <v>245.3</v>
       </c>
       <c r="L2">
-        <v>-3.087310954354569</v>
+        <v>2.24510342302764</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>28.235</v>
+        <v>28.35</v>
       </c>
       <c r="V2">
-        <v>0.3705380577427821</v>
+        <v>0.4056490384615385</v>
       </c>
       <c r="W2">
-        <v>0.2043441156278757</v>
+        <v>-0.1757469244288225</v>
       </c>
       <c r="X2">
-        <v>2.091019029474091</v>
+        <v>0.72700683113499</v>
       </c>
       <c r="Y2">
-        <v>-1.886674913846215</v>
+        <v>-0.9027537555638125</v>
       </c>
       <c r="Z2">
-        <v>0.1218613827597241</v>
+        <v>0.4124949032754949</v>
       </c>
       <c r="AA2">
-        <v>-0.007003577851176317</v>
+        <v>-0.1756141947224749</v>
       </c>
       <c r="AB2">
-        <v>0.06372848618896086</v>
+        <v>0.06922602039653523</v>
       </c>
       <c r="AC2">
-        <v>-0.07073206404013718</v>
+        <v>-0.3135300012936856</v>
       </c>
       <c r="AD2">
-        <v>551.9</v>
+        <v>348</v>
       </c>
       <c r="AE2">
-        <v>1.390840268861083</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>553.2908402688611</v>
+        <v>348</v>
       </c>
       <c r="AG2">
-        <v>525.0558402688611</v>
+        <v>319.65</v>
       </c>
       <c r="AH2">
-        <v>0.8789497874703716</v>
+        <v>0.8327590167700437</v>
       </c>
       <c r="AI2">
-        <v>1.922544997443155</v>
+        <v>1.234918381831086</v>
       </c>
       <c r="AJ2">
-        <v>0.8732652643075766</v>
+        <v>0.8205874651510251</v>
       </c>
       <c r="AK2">
-        <v>2.022901275213001</v>
+        <v>1.261195502071415</v>
       </c>
       <c r="AL2">
-        <v>106.15</v>
+        <v>44.331</v>
       </c>
       <c r="AM2">
-        <v>106.15</v>
+        <v>37.794</v>
       </c>
       <c r="AN2">
-        <v>-277.3366834170854</v>
+        <v>-22.77635970940507</v>
       </c>
       <c r="AO2">
-        <v>-0.03127649552520019</v>
+        <v>-0.5037783943515824</v>
       </c>
       <c r="AP2">
-        <v>-263.8471559140005</v>
+        <v>-20.92087178480267</v>
       </c>
       <c r="AQ2">
-        <v>-0.03127649552520019</v>
+        <v>-0.5909139016775149</v>
       </c>
     </row>
     <row r="3">
@@ -715,23 +715,26 @@
           <t>Real Estate (General/Diversified)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>1.138</v>
+      </c>
       <c r="G3">
-        <v>-40.90909090909091</v>
+        <v>0.1261904761904762</v>
       </c>
       <c r="H3">
-        <v>-40.90909090909091</v>
+        <v>0.1261904761904762</v>
       </c>
       <c r="I3">
-        <v>-45.75757575757576</v>
+        <v>-0.3277777777777778</v>
       </c>
       <c r="J3">
-        <v>-45.75757575757576</v>
+        <v>-0.3277777777777778</v>
       </c>
       <c r="K3">
-        <v>-3.78</v>
+        <v>-20</v>
       </c>
       <c r="L3">
-        <v>-114.5454545454545</v>
+        <v>-15.87301587301587</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.035</v>
+        <v>5.62</v>
       </c>
       <c r="V3">
-        <v>0.0004736129905277402</v>
+        <v>0.08567073170731708</v>
       </c>
       <c r="W3">
-        <v>-0.03390134529147982</v>
+        <v>-0.1757469244288225</v>
       </c>
       <c r="X3">
-        <v>0.05039098281733335</v>
+        <v>0.08346793113546108</v>
       </c>
       <c r="Y3">
-        <v>-0.08429232810881317</v>
+        <v>-0.2592148555642836</v>
       </c>
       <c r="Z3">
-        <v>0.0002243676910524884</v>
+        <v>0.008130291141854222</v>
       </c>
       <c r="AA3">
-        <v>-0.01026652162088659</v>
+        <v>-0.002664928763163329</v>
       </c>
       <c r="AB3">
-        <v>0.03958590123926178</v>
+        <v>0.06922602039653523</v>
       </c>
       <c r="AC3">
-        <v>-0.04985242286014837</v>
+        <v>-0.07189094915969857</v>
       </c>
       <c r="AD3">
-        <v>42.9</v>
+        <v>36.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>42.9</v>
+        <v>36.5</v>
       </c>
       <c r="AG3">
-        <v>42.865</v>
+        <v>30.88</v>
       </c>
       <c r="AH3">
-        <v>0.3672945205479451</v>
+        <v>0.3574926542605289</v>
       </c>
       <c r="AI3">
-        <v>0.2671232876712329</v>
+        <v>0.3125</v>
       </c>
       <c r="AJ3">
-        <v>0.3671048687534792</v>
+        <v>0.3200663349917082</v>
       </c>
       <c r="AK3">
-        <v>0.2669635350169713</v>
+        <v>0.2777477963662529</v>
       </c>
       <c r="AL3">
-        <v>3.45</v>
+        <v>0.031</v>
       </c>
       <c r="AM3">
-        <v>3.45</v>
+        <v>0.028</v>
       </c>
       <c r="AN3">
-        <v>-31.77777777777778</v>
+        <v>-96.30606860158311</v>
       </c>
       <c r="AO3">
-        <v>-0.4376811594202898</v>
+        <v>-13.32258064516129</v>
       </c>
       <c r="AP3">
-        <v>-31.75185185185185</v>
+        <v>-81.47757255936675</v>
       </c>
       <c r="AQ3">
-        <v>-0.4376811594202898</v>
+        <v>-14.75</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kardan N.V. (TASE:KRNV)</t>
+          <t>Kardan N.V. (TASE:KRNV-M)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.08789999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="G4">
-        <v>0.0104945054945055</v>
+        <v>-0.2212962962962963</v>
       </c>
       <c r="H4">
-        <v>0.0104945054945055</v>
+        <v>-0.2212962962962963</v>
       </c>
       <c r="I4">
-        <v>-0.01560901246626969</v>
+        <v>-0.1787037037037037</v>
       </c>
       <c r="J4">
-        <v>-0.01560901246626969</v>
+        <v>-0.1787037037037037</v>
       </c>
       <c r="K4">
-        <v>-108.7</v>
+        <v>290.8</v>
       </c>
       <c r="L4">
-        <v>-2.986263736263736</v>
+        <v>2.692592592592593</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -868,7 +871,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -877,79 +880,174 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>28.2</v>
+        <v>19.4</v>
       </c>
       <c r="V4">
-        <v>12.26086956521739</v>
+        <v>34.76702508960573</v>
       </c>
       <c r="W4">
-        <v>0.4425895765472313</v>
+        <v>-0.7840388244809923</v>
       </c>
       <c r="X4">
-        <v>4.131647076130848</v>
+        <v>8.777031650474161</v>
       </c>
       <c r="Y4">
-        <v>-3.689057499583617</v>
+        <v>-9.561070474955153</v>
       </c>
       <c r="Z4">
-        <v>0.2396457873007258</v>
+        <v>0.9827115559599634</v>
       </c>
       <c r="AA4">
-        <v>-0.003740634081466043</v>
+        <v>-0.1756141947224749</v>
       </c>
       <c r="AB4">
-        <v>0.08787107113865995</v>
+        <v>0.1379158065712107</v>
       </c>
       <c r="AC4">
-        <v>-0.091611705220126</v>
+        <v>-0.3135300012936856</v>
       </c>
       <c r="AD4">
-        <v>509</v>
+        <v>207.1</v>
       </c>
       <c r="AE4">
-        <v>1.390840268861083</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>510.3908402688611</v>
+        <v>207.1</v>
       </c>
       <c r="AG4">
-        <v>482.1908402688611</v>
+        <v>187.7</v>
       </c>
       <c r="AH4">
-        <v>0.9955138656294429</v>
+        <v>0.9973128894624816</v>
       </c>
       <c r="AI4">
-        <v>4.012795569161871</v>
+        <v>1.121885157096425</v>
       </c>
       <c r="AJ4">
-        <v>0.9952527482279672</v>
+        <v>0.9970359825346068</v>
       </c>
       <c r="AK4">
-        <v>4.871065231482237</v>
+        <v>1.136198547215496</v>
       </c>
       <c r="AL4">
-        <v>102.7</v>
+        <v>36</v>
       </c>
       <c r="AM4">
-        <v>102.7</v>
+        <v>30.39</v>
       </c>
       <c r="AN4">
-        <v>-795.3124999999999</v>
+        <v>-13.8993288590604</v>
       </c>
       <c r="AO4">
-        <v>-0.01762414800389484</v>
+        <v>-0.5361111111111111</v>
       </c>
       <c r="AP4">
-        <v>-753.4231879200953</v>
+        <v>-12.59731543624161</v>
       </c>
       <c r="AQ4">
-        <v>-0.01762414800389484</v>
+        <v>-0.6350773280684435</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Plaza Centers N.V. (LSE:PLAZ)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Real Estate (General/Diversified)</t>
+        </is>
+      </c>
+      <c r="K5">
+        <v>-25.5</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>3.33</v>
+      </c>
+      <c r="V5">
+        <v>0.8927613941018767</v>
+      </c>
+      <c r="W5">
+        <v>0.2276785714285714</v>
+      </c>
+      <c r="X5">
+        <v>0.72700683113499</v>
+      </c>
+      <c r="Y5">
+        <v>-0.4993282597064186</v>
+      </c>
+      <c r="AB5">
+        <v>0.06720304929375302</v>
+      </c>
+      <c r="AD5">
+        <v>104.4</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>104.4</v>
+      </c>
+      <c r="AG5">
+        <v>101.07</v>
+      </c>
+      <c r="AH5">
+        <v>0.9655044853417183</v>
+      </c>
+      <c r="AI5">
+        <v>-5.3265306122449</v>
+      </c>
+      <c r="AJ5">
+        <v>0.9644083969465649</v>
+      </c>
+      <c r="AK5">
+        <v>-4.407762756214568</v>
+      </c>
+      <c r="AL5">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AM5">
+        <v>7.376</v>
+      </c>
+      <c r="AO5">
+        <v>-0.3156626506024096</v>
+      </c>
+      <c r="AQ5">
+        <v>-0.3552060737527115</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_real_estate_general_diversified.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.889</v>
+        <v>0.4566</v>
       </c>
       <c r="G2">
-        <v>-0.217289035328574</v>
+        <v>-0.2740975803252678</v>
       </c>
       <c r="H2">
-        <v>-0.217289035328574</v>
+        <v>-0.2740975803252678</v>
       </c>
       <c r="I2">
-        <v>-0.2044023430349625</v>
+        <v>-0.3093021528758373</v>
       </c>
       <c r="J2">
-        <v>-0.2044023430349625</v>
+        <v>-0.3093021528758373</v>
       </c>
       <c r="K2">
-        <v>245.3</v>
+        <v>-102.6</v>
       </c>
       <c r="L2">
-        <v>2.24510342302764</v>
+        <v>-1.017453391511305</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>28.35</v>
+        <v>44.90000000000001</v>
       </c>
       <c r="V2">
-        <v>0.4056490384615385</v>
+        <v>0.8764909129951004</v>
       </c>
       <c r="W2">
-        <v>-0.1757469244288225</v>
+        <v>2.748478405564317</v>
       </c>
       <c r="X2">
-        <v>0.72700683113499</v>
+        <v>4.883621787993893</v>
       </c>
       <c r="Y2">
-        <v>-0.9027537555638125</v>
+        <v>-2.135143382429576</v>
       </c>
       <c r="Z2">
-        <v>0.4124949032754949</v>
+        <v>0.2742563882159496</v>
       </c>
       <c r="AA2">
-        <v>-0.1756141947224749</v>
+        <v>-0.08638689218478907</v>
       </c>
       <c r="AB2">
-        <v>0.06922602039653523</v>
+        <v>0.06826326389449383</v>
       </c>
       <c r="AC2">
-        <v>-0.3135300012936856</v>
+        <v>-0.1546501560792829</v>
       </c>
       <c r="AD2">
-        <v>348</v>
+        <v>174.96</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.565145479997188</v>
       </c>
       <c r="AF2">
-        <v>348</v>
+        <v>175.5251454799972</v>
       </c>
       <c r="AG2">
-        <v>319.65</v>
+        <v>130.6251454799972</v>
       </c>
       <c r="AH2">
-        <v>0.8327590167700437</v>
+        <v>0.7740837252429924</v>
       </c>
       <c r="AI2">
-        <v>1.234918381831086</v>
+        <v>0.9723030274441518</v>
       </c>
       <c r="AJ2">
-        <v>0.8205874651510251</v>
+        <v>0.718304120829662</v>
       </c>
       <c r="AK2">
-        <v>1.261195502071415</v>
+        <v>0.9631336800981538</v>
       </c>
       <c r="AL2">
-        <v>44.331</v>
+        <v>59.255</v>
       </c>
       <c r="AM2">
-        <v>37.794</v>
+        <v>59.255</v>
       </c>
       <c r="AN2">
-        <v>-22.77635970940507</v>
+        <v>-6.06089998960751</v>
       </c>
       <c r="AO2">
-        <v>-0.5037783943515824</v>
+        <v>-0.5307568981520546</v>
       </c>
       <c r="AP2">
-        <v>-20.92087178480267</v>
+        <v>-4.525068260643544</v>
       </c>
       <c r="AQ2">
-        <v>-0.5909139016775149</v>
+        <v>-0.5307568981520546</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.138</v>
+        <v>0.885</v>
       </c>
       <c r="G3">
-        <v>0.1261904761904762</v>
+        <v>-0.912280701754386</v>
       </c>
       <c r="H3">
-        <v>0.1261904761904762</v>
+        <v>-0.912280701754386</v>
       </c>
       <c r="I3">
-        <v>-0.3277777777777778</v>
+        <v>-0.9210526315789475</v>
       </c>
       <c r="J3">
-        <v>-0.3277777777777778</v>
+        <v>-0.9210526315789475</v>
       </c>
       <c r="K3">
-        <v>-20</v>
+        <v>-55.9</v>
       </c>
       <c r="L3">
-        <v>-15.87301587301587</v>
+        <v>-49.03508771929825</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.62</v>
+        <v>33.2</v>
       </c>
       <c r="V3">
-        <v>0.08567073170731708</v>
+        <v>0.6522593320235757</v>
       </c>
       <c r="W3">
-        <v>-0.1757469244288225</v>
+        <v>-0.3625162127107653</v>
       </c>
       <c r="X3">
-        <v>0.08346793113546108</v>
+        <v>0.06313415882792607</v>
       </c>
       <c r="Y3">
-        <v>-0.2592148555642836</v>
+        <v>-0.4256503715386913</v>
       </c>
       <c r="Z3">
-        <v>0.008130291141854222</v>
+        <v>0.006083569027162602</v>
       </c>
       <c r="AA3">
-        <v>-0.002664928763163329</v>
+        <v>-0.005603287261860292</v>
       </c>
       <c r="AB3">
-        <v>0.06922602039653523</v>
+        <v>0.06301513945311644</v>
       </c>
       <c r="AC3">
-        <v>-0.07189094915969857</v>
+        <v>-0.06861842671497674</v>
       </c>
       <c r="AD3">
-        <v>36.5</v>
+        <v>0.26</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>36.5</v>
+        <v>0.26</v>
       </c>
       <c r="AG3">
-        <v>30.88</v>
+        <v>-32.94</v>
       </c>
       <c r="AH3">
-        <v>0.3574926542605289</v>
+        <v>0.00508209538702111</v>
       </c>
       <c r="AI3">
-        <v>0.3125</v>
+        <v>0.002912838897602509</v>
       </c>
       <c r="AJ3">
-        <v>0.3200663349917082</v>
+        <v>-1.834075723830736</v>
       </c>
       <c r="AK3">
-        <v>0.2777477963662529</v>
+        <v>-0.5875847306457368</v>
       </c>
       <c r="AL3">
-        <v>0.031</v>
+        <v>0.055</v>
       </c>
       <c r="AM3">
-        <v>0.028</v>
+        <v>0.055</v>
       </c>
       <c r="AN3">
-        <v>-96.30606860158311</v>
+        <v>-0.25</v>
       </c>
       <c r="AO3">
-        <v>-13.32258064516129</v>
+        <v>-19.09090909090909</v>
       </c>
       <c r="AP3">
-        <v>-81.47757255936675</v>
+        <v>31.67307692307693</v>
       </c>
       <c r="AQ3">
-        <v>-14.75</v>
+        <v>-19.09090909090909</v>
       </c>
     </row>
     <row r="4">
@@ -844,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.64</v>
+        <v>0.0282</v>
       </c>
       <c r="G4">
-        <v>-0.2212962962962963</v>
+        <v>-0.2668004012036108</v>
       </c>
       <c r="H4">
-        <v>-0.2212962962962963</v>
+        <v>-0.2668004012036108</v>
       </c>
       <c r="I4">
-        <v>-0.1787037037037037</v>
+        <v>-0.3023072125977877</v>
       </c>
       <c r="J4">
-        <v>-0.1787037037037037</v>
+        <v>-0.3023072125977877</v>
       </c>
       <c r="K4">
-        <v>290.8</v>
+        <v>-46.7</v>
       </c>
       <c r="L4">
-        <v>2.692592592592593</v>
+        <v>-0.4684052156469408</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -871,7 +871,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -880,174 +880,79 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>19.4</v>
+        <v>11.7</v>
       </c>
       <c r="V4">
-        <v>34.76702508960573</v>
+        <v>35.77981651376147</v>
       </c>
       <c r="W4">
-        <v>-0.7840388244809923</v>
+        <v>5.859473023839398</v>
       </c>
       <c r="X4">
-        <v>8.777031650474161</v>
+        <v>9.704109417159859</v>
       </c>
       <c r="Y4">
-        <v>-9.561070474955153</v>
+        <v>-3.844636393320461</v>
       </c>
       <c r="Z4">
-        <v>0.9827115559599634</v>
+        <v>0.552982165629419</v>
       </c>
       <c r="AA4">
-        <v>-0.1756141947224749</v>
+        <v>-0.1671704971077178</v>
       </c>
       <c r="AB4">
-        <v>0.1379158065712107</v>
+        <v>0.07351138833587122</v>
       </c>
       <c r="AC4">
-        <v>-0.3135300012936856</v>
+        <v>-0.240681885443589</v>
       </c>
       <c r="AD4">
-        <v>207.1</v>
+        <v>174.7</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.565145479997188</v>
       </c>
       <c r="AF4">
-        <v>207.1</v>
+        <v>175.2651454799972</v>
       </c>
       <c r="AG4">
-        <v>187.7</v>
+        <v>163.5651454799972</v>
       </c>
       <c r="AH4">
-        <v>0.9973128894624816</v>
+        <v>0.9981377299132252</v>
       </c>
       <c r="AI4">
-        <v>1.121885157096425</v>
+        <v>1.920395179980407</v>
       </c>
       <c r="AJ4">
-        <v>0.9970359825346068</v>
+        <v>0.9980047854090731</v>
       </c>
       <c r="AK4">
-        <v>1.136198547215496</v>
+        <v>2.055738659098131</v>
       </c>
       <c r="AL4">
-        <v>36</v>
+        <v>59.2</v>
       </c>
       <c r="AM4">
-        <v>30.39</v>
+        <v>59.2</v>
       </c>
       <c r="AN4">
-        <v>-13.8993288590604</v>
+        <v>-6.278075250655838</v>
       </c>
       <c r="AO4">
-        <v>-0.5361111111111111</v>
+        <v>-0.5135135135135135</v>
       </c>
       <c r="AP4">
-        <v>-12.59731543624161</v>
+        <v>-5.877929546124167</v>
       </c>
       <c r="AQ4">
-        <v>-0.6350773280684435</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Plaza Centers N.V. (LSE:PLAZ)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Real Estate (General/Diversified)</t>
-        </is>
-      </c>
-      <c r="K5">
-        <v>-25.5</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>3.33</v>
-      </c>
-      <c r="V5">
-        <v>0.8927613941018767</v>
-      </c>
-      <c r="W5">
-        <v>0.2276785714285714</v>
-      </c>
-      <c r="X5">
-        <v>0.72700683113499</v>
-      </c>
-      <c r="Y5">
-        <v>-0.4993282597064186</v>
-      </c>
-      <c r="AB5">
-        <v>0.06720304929375302</v>
-      </c>
-      <c r="AD5">
-        <v>104.4</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>104.4</v>
-      </c>
-      <c r="AG5">
-        <v>101.07</v>
-      </c>
-      <c r="AH5">
-        <v>0.9655044853417183</v>
-      </c>
-      <c r="AI5">
-        <v>-5.3265306122449</v>
-      </c>
-      <c r="AJ5">
-        <v>0.9644083969465649</v>
-      </c>
-      <c r="AK5">
-        <v>-4.407762756214568</v>
-      </c>
-      <c r="AL5">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AM5">
-        <v>7.376</v>
-      </c>
-      <c r="AO5">
-        <v>-0.3156626506024096</v>
-      </c>
-      <c r="AQ5">
-        <v>-0.3552060737527115</v>
+        <v>-0.5135135135135135</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_real_estate_general_diversified.xlsx
@@ -1263,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1400,22 +1400,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0686193600957969</v>
+        <v>0.06847571214674976</v>
       </c>
       <c r="C2">
-        <v>185.7564622850002</v>
+        <v>183.9107245538257</v>
       </c>
       <c r="D2">
-        <v>176.1164622850002</v>
+        <v>177.232139201207</v>
       </c>
       <c r="E2">
-        <v>-295.8784647381358</v>
+        <v>-292.9170500907545</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.961414647381358</v>
       </c>
       <c r="G2">
         <v>9.640000000000001</v>
@@ -1436,28 +1436,28 @@
         <v>2.574</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1489591567632823</v>
       </c>
       <c r="N2">
-        <v>2.574</v>
+        <v>2.425040843236717</v>
       </c>
       <c r="O2">
-        <v>0.664092</v>
+        <v>0.6256605375550731</v>
       </c>
       <c r="P2">
-        <v>1.909908</v>
+        <v>1.799380305681644</v>
       </c>
       <c r="Q2">
-        <v>2.321908</v>
+        <v>2.211380305681644</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0686193600957969</v>
+        <v>0.06879039004722197</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313372</v>
+        <v>0.5309558902360731</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>17.27990447804736</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1482,22 +1482,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06847571214674976</v>
+        <v>0.06837955219770259</v>
       </c>
       <c r="C3">
-        <v>183.9107245538257</v>
+        <v>181.7040916366525</v>
       </c>
       <c r="D3">
-        <v>177.232139201207</v>
+        <v>177.9869209314153</v>
       </c>
       <c r="E3">
-        <v>-292.9170500907545</v>
+        <v>-289.9556354433731</v>
       </c>
       <c r="F3">
-        <v>2.961414647381358</v>
+        <v>5.922829294762716</v>
       </c>
       <c r="G3">
         <v>9.640000000000001</v>
@@ -1518,45 +1518,45 @@
         <v>2.574</v>
       </c>
       <c r="M3">
-        <v>0.1489591567632823</v>
+        <v>0.3168713672698053</v>
       </c>
       <c r="N3">
-        <v>2.425040843236717</v>
+        <v>2.257128632730195</v>
       </c>
       <c r="O3">
-        <v>0.6256605375550731</v>
+        <v>0.5823391872443903</v>
       </c>
       <c r="P3">
-        <v>1.799380305681644</v>
+        <v>1.674789445485804</v>
       </c>
       <c r="Q3">
-        <v>2.211380305681644</v>
+        <v>2.086789445485804</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06879039004722197</v>
+        <v>0.06896491040581897</v>
       </c>
       <c r="T3">
-        <v>0.5309558902360731</v>
+        <v>0.5349863835062117</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0373226</v>
+        <v>0.039697</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y3">
-        <v>17.27990447804736</v>
+        <v>8.123170049026001</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1564,22 +1564,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06837955219770259</v>
+        <v>0.06829971624865543</v>
       </c>
       <c r="C4">
-        <v>181.7040916366525</v>
+        <v>179.3742296094688</v>
       </c>
       <c r="D4">
-        <v>177.9869209314153</v>
+        <v>178.6184735516129</v>
       </c>
       <c r="E4">
-        <v>-289.9556354433731</v>
+        <v>-286.9942207959917</v>
       </c>
       <c r="F4">
-        <v>5.922829294762716</v>
+        <v>8.884243942144073</v>
       </c>
       <c r="G4">
         <v>9.640000000000001</v>
@@ -1600,45 +1600,45 @@
         <v>2.574</v>
       </c>
       <c r="M4">
-        <v>0.3168713672698053</v>
+        <v>0.4912986900005673</v>
       </c>
       <c r="N4">
-        <v>2.257128632730195</v>
+        <v>2.082701309999432</v>
       </c>
       <c r="O4">
-        <v>0.5823391872443903</v>
+        <v>0.5373369379798536</v>
       </c>
       <c r="P4">
-        <v>1.674789445485804</v>
+        <v>1.545364372019579</v>
       </c>
       <c r="Q4">
-        <v>2.086789445485804</v>
+        <v>1.957364372019579</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06896491040581897</v>
+        <v>0.06914302912232519</v>
       </c>
       <c r="T4">
-        <v>0.5349863835062117</v>
+        <v>0.5390999797303739</v>
       </c>
       <c r="U4">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.039697</v>
+        <v>0.0410326</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y4">
-        <v>8.123170049026001</v>
+        <v>5.239175378214479</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06829971624865543</v>
+        <v>0.06837124829960826</v>
       </c>
       <c r="C5">
-        <v>179.3742296094688</v>
+        <v>175.8467432242016</v>
       </c>
       <c r="D5">
-        <v>178.6184735516129</v>
+        <v>178.0524018137271</v>
       </c>
       <c r="E5">
-        <v>-286.9942207959917</v>
+        <v>-284.0328061486103</v>
       </c>
       <c r="F5">
-        <v>8.884243942144073</v>
+        <v>11.84565858952543</v>
       </c>
       <c r="G5">
         <v>9.640000000000001</v>
@@ -1682,45 +1682,45 @@
         <v>2.574</v>
       </c>
       <c r="M5">
-        <v>0.4912986900005673</v>
+        <v>0.7261388715379089</v>
       </c>
       <c r="N5">
-        <v>2.082701309999432</v>
+        <v>1.847861128462091</v>
       </c>
       <c r="O5">
-        <v>0.5373369379798536</v>
+        <v>0.4767481711432195</v>
       </c>
       <c r="P5">
-        <v>1.545364372019579</v>
+        <v>1.371112957318871</v>
       </c>
       <c r="Q5">
-        <v>1.957364372019579</v>
+        <v>1.783112957318871</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06914302912232519</v>
+        <v>0.06932485864542529</v>
       </c>
       <c r="T5">
-        <v>0.5390999797303739</v>
+        <v>0.5432992758758728</v>
       </c>
       <c r="U5">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0410326</v>
+        <v>0.0454846</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>5.239175378214479</v>
+        <v>3.544776489583124</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1728,22 +1728,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06837124829960826</v>
+        <v>0.06884717035056112</v>
       </c>
       <c r="C6">
-        <v>175.8467432242016</v>
+        <v>169.208562060179</v>
       </c>
       <c r="D6">
-        <v>178.0524018137271</v>
+        <v>174.3756352970858</v>
       </c>
       <c r="E6">
-        <v>-284.0328061486103</v>
+        <v>-281.071391501229</v>
       </c>
       <c r="F6">
-        <v>11.84565858952543</v>
+        <v>14.80707323690679</v>
       </c>
       <c r="G6">
         <v>9.640000000000001</v>
@@ -1764,45 +1764,45 @@
         <v>2.574</v>
       </c>
       <c r="M6">
-        <v>0.7261388715379089</v>
+        <v>1.122376151357535</v>
       </c>
       <c r="N6">
-        <v>1.847861128462091</v>
+        <v>1.451623848642465</v>
       </c>
       <c r="O6">
-        <v>0.4767481711432195</v>
+        <v>0.3745189529497561</v>
       </c>
       <c r="P6">
-        <v>1.371112957318871</v>
+        <v>1.077104895692709</v>
       </c>
       <c r="Q6">
-        <v>1.783112957318871</v>
+        <v>1.489104895692709</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06932485864542529</v>
+        <v>0.0695105161584854</v>
       </c>
       <c r="T6">
-        <v>0.5432992758758728</v>
+        <v>0.5475869782560138</v>
       </c>
       <c r="U6">
-        <v>0.0613</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0454846</v>
+        <v>0.0562436</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y6">
-        <v>3.544776489583124</v>
+        <v>2.293348800120797</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1810,22 +1810,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06884717035056112</v>
+        <v>0.06952491640151397</v>
       </c>
       <c r="C7">
-        <v>169.208562060179</v>
+        <v>161.2657853626682</v>
       </c>
       <c r="D7">
-        <v>174.3756352970858</v>
+        <v>169.3942732469564</v>
       </c>
       <c r="E7">
-        <v>-281.071391501229</v>
+        <v>-278.1099768538476</v>
       </c>
       <c r="F7">
-        <v>14.80707323690679</v>
+        <v>17.76848788428815</v>
       </c>
       <c r="G7">
         <v>9.640000000000001</v>
@@ -1846,45 +1846,45 @@
         <v>2.574</v>
       </c>
       <c r="M7">
-        <v>1.122376151357535</v>
+        <v>1.599163909585933</v>
       </c>
       <c r="N7">
-        <v>1.451623848642465</v>
+        <v>0.9748360904140665</v>
       </c>
       <c r="O7">
-        <v>0.3745189529497561</v>
+        <v>0.2515077113268291</v>
       </c>
       <c r="P7">
-        <v>1.077104895692709</v>
+        <v>0.7233283790872373</v>
       </c>
       <c r="Q7">
-        <v>1.489104895692709</v>
+        <v>1.135328379087237</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0695105161584854</v>
+        <v>0.06970012383139784</v>
       </c>
       <c r="T7">
-        <v>0.5475869782560138</v>
+        <v>0.5519659083463704</v>
       </c>
       <c r="U7">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>2.293348800120797</v>
+        <v>1.609591102307004</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1892,22 +1892,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06952491640151397</v>
+        <v>0.07309829458641055</v>
       </c>
       <c r="C8">
-        <v>161.2657853626683</v>
+        <v>136.1304653546049</v>
       </c>
       <c r="D8">
-        <v>169.3942732469564</v>
+        <v>147.2203678862744</v>
       </c>
       <c r="E8">
-        <v>-278.1099768538476</v>
+        <v>-275.1485622064663</v>
       </c>
       <c r="F8">
-        <v>17.76848788428815</v>
+        <v>20.7299025316695</v>
       </c>
       <c r="G8">
         <v>9.640000000000001</v>
@@ -1928,45 +1928,45 @@
         <v>2.574</v>
       </c>
       <c r="M8">
-        <v>1.599163909585933</v>
+        <v>3.043149691649083</v>
       </c>
       <c r="N8">
-        <v>0.9748360904140669</v>
+        <v>-0.4691496916490832</v>
       </c>
       <c r="O8">
-        <v>0.2515077113268293</v>
+        <v>-0.1210406204454635</v>
       </c>
       <c r="P8">
-        <v>0.7233283790872377</v>
+        <v>-0.3481090712036197</v>
       </c>
       <c r="Q8">
-        <v>1.135328379087237</v>
+        <v>0.06389092879638025</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06970012383139784</v>
+        <v>0.06996212570983298</v>
       </c>
       <c r="T8">
-        <v>0.5519659083463704</v>
+        <v>0.558016760042332</v>
       </c>
       <c r="U8">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V8">
-        <v>0.258</v>
+        <v>0.218225216400751</v>
       </c>
       <c r="W8">
-        <v>0.06677999999999999</v>
+        <v>0.1147645382323698</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y8">
-        <v>1.609591102307004</v>
+        <v>0.8458341720959343</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1974,22 +1974,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07309829458641055</v>
+        <v>0.078522037076576</v>
       </c>
       <c r="C9">
-        <v>136.1304653546049</v>
+        <v>108.7669829858906</v>
       </c>
       <c r="D9">
-        <v>147.2203678862744</v>
+        <v>122.8183001649415</v>
       </c>
       <c r="E9">
-        <v>-275.1485622064663</v>
+        <v>-272.1871475590849</v>
       </c>
       <c r="F9">
-        <v>20.72990253166951</v>
+        <v>23.69131717905086</v>
       </c>
       <c r="G9">
         <v>9.640000000000001</v>
@@ -2010,45 +2010,45 @@
         <v>2.574</v>
       </c>
       <c r="M9">
-        <v>3.043149691649084</v>
+        <v>4.757216489553413</v>
       </c>
       <c r="N9">
-        <v>-0.469149691649084</v>
+        <v>-2.183216489553414</v>
       </c>
       <c r="O9">
-        <v>-0.1210406204454637</v>
+        <v>-0.5632698543047807</v>
       </c>
       <c r="P9">
-        <v>-0.3481090712036203</v>
+        <v>-1.619946635248633</v>
       </c>
       <c r="Q9">
-        <v>0.06389092879637959</v>
+        <v>-1.207946635248633</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06996212570983298</v>
+        <v>0.07032665152207621</v>
       </c>
       <c r="T9">
-        <v>0.558016760042332</v>
+        <v>0.5664353700248546</v>
       </c>
       <c r="U9">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V9">
-        <v>0.218225216400751</v>
+        <v>0.13959675820058</v>
       </c>
       <c r="W9">
-        <v>0.1147645382323698</v>
+        <v>0.1727689709533235</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y9">
-        <v>0.845834172095934</v>
+        <v>0.5410727062037985</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2056,22 +2056,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.078522037076576</v>
+        <v>0.08325986330364145</v>
       </c>
       <c r="C10">
-        <v>108.7669829858906</v>
+        <v>90.27182869380287</v>
       </c>
       <c r="D10">
-        <v>122.8183001649415</v>
+        <v>107.2845605202351</v>
       </c>
       <c r="E10">
-        <v>-272.1871475590849</v>
+        <v>-269.2257329117036</v>
       </c>
       <c r="F10">
-        <v>23.69131717905086</v>
+        <v>26.65273182643222</v>
       </c>
       <c r="G10">
         <v>9.640000000000001</v>
@@ -2092,45 +2092,45 @@
         <v>2.574</v>
       </c>
       <c r="M10">
-        <v>4.757216489553413</v>
+        <v>6.284714164672717</v>
       </c>
       <c r="N10">
-        <v>-2.183216489553414</v>
+        <v>-3.710714164672718</v>
       </c>
       <c r="O10">
-        <v>-0.5632698543047807</v>
+        <v>-0.9573642544855612</v>
       </c>
       <c r="P10">
-        <v>-1.619946635248633</v>
+        <v>-2.753349910187156</v>
       </c>
       <c r="Q10">
-        <v>-1.207946635248633</v>
+        <v>-2.341349910187156</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07032665152207621</v>
+        <v>0.07063774244766546</v>
       </c>
       <c r="T10">
-        <v>0.5664353700248546</v>
+        <v>0.5736199179599416</v>
       </c>
       <c r="U10">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.13959675820058</v>
+        <v>0.1056678128232079</v>
       </c>
       <c r="W10">
-        <v>0.1727689709533235</v>
+        <v>0.2108835297362876</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y10">
-        <v>0.5410727062037985</v>
+        <v>0.4095651659814259</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2138,22 +2138,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08325986330364145</v>
+        <v>0.08515986330364146</v>
       </c>
       <c r="C11">
-        <v>90.27182869380287</v>
+        <v>82.13151737658504</v>
       </c>
       <c r="D11">
-        <v>107.2845605202351</v>
+        <v>102.1056638503986</v>
       </c>
       <c r="E11">
-        <v>-269.2257329117036</v>
+        <v>-266.2643182643222</v>
       </c>
       <c r="F11">
-        <v>26.65273182643222</v>
+        <v>29.61414647381357</v>
       </c>
       <c r="G11">
         <v>9.640000000000001</v>
@@ -2174,37 +2174,37 @@
         <v>2.574</v>
       </c>
       <c r="M11">
-        <v>6.284714164672717</v>
+        <v>6.983015738525241</v>
       </c>
       <c r="N11">
-        <v>-3.710714164672718</v>
+        <v>-4.409015738525241</v>
       </c>
       <c r="O11">
-        <v>-0.9573642544855612</v>
+        <v>-1.137526060539512</v>
       </c>
       <c r="P11">
-        <v>-2.753349910187156</v>
+        <v>-3.271489677985729</v>
       </c>
       <c r="Q11">
-        <v>-2.341349910187156</v>
+        <v>-2.859489677985729</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07063774244766546</v>
+        <v>0.07091371736375064</v>
       </c>
       <c r="T11">
-        <v>0.5736199179599416</v>
+        <v>0.5799934726039409</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.1056678128232079</v>
+        <v>0.0951010315408871</v>
       </c>
       <c r="W11">
-        <v>0.2108835297362876</v>
+        <v>0.2133751767626588</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.4095651659814259</v>
+        <v>0.3686086493832833</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2220,22 +2220,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08515986330364148</v>
+        <v>0.08705986330364147</v>
       </c>
       <c r="C12">
-        <v>82.13151737658501</v>
+        <v>74.46817824903613</v>
       </c>
       <c r="D12">
-        <v>102.1056638503986</v>
+        <v>97.40373937023107</v>
       </c>
       <c r="E12">
-        <v>-266.2643182643222</v>
+        <v>-263.3029036169409</v>
       </c>
       <c r="F12">
-        <v>29.61414647381358</v>
+        <v>32.57556112119494</v>
       </c>
       <c r="G12">
         <v>9.640000000000001</v>
@@ -2256,37 +2256,37 @@
         <v>2.574</v>
       </c>
       <c r="M12">
-        <v>6.983015738525242</v>
+        <v>7.681317312377766</v>
       </c>
       <c r="N12">
-        <v>-4.409015738525242</v>
+        <v>-5.107317312377766</v>
       </c>
       <c r="O12">
-        <v>-1.137526060539513</v>
+        <v>-1.317687866593464</v>
       </c>
       <c r="P12">
-        <v>-3.27148967798573</v>
+        <v>-3.789629445784302</v>
       </c>
       <c r="Q12">
-        <v>-2.85948967798573</v>
+        <v>-3.377629445784303</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07091371736375064</v>
+        <v>0.07119589396334335</v>
       </c>
       <c r="T12">
-        <v>0.5799934726039409</v>
+        <v>0.5865102531949964</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.0951010315408871</v>
+        <v>0.08645548321898826</v>
       </c>
       <c r="W12">
-        <v>0.2133751767626588</v>
+        <v>0.2154137970569626</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.3686086493832833</v>
+        <v>0.3350987721666212</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2302,22 +2302,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08705986330364147</v>
+        <v>0.08895986330364145</v>
       </c>
       <c r="C13">
-        <v>74.46817824903613</v>
+        <v>67.21881895499453</v>
       </c>
       <c r="D13">
-        <v>97.40373937023107</v>
+        <v>93.11579472357083</v>
       </c>
       <c r="E13">
-        <v>-263.3029036169409</v>
+        <v>-260.3414889695595</v>
       </c>
       <c r="F13">
-        <v>32.57556112119494</v>
+        <v>35.53697576857629</v>
       </c>
       <c r="G13">
         <v>9.640000000000001</v>
@@ -2338,37 +2338,37 @@
         <v>2.574</v>
       </c>
       <c r="M13">
-        <v>7.681317312377766</v>
+        <v>8.37961888623029</v>
       </c>
       <c r="N13">
-        <v>-5.107317312377766</v>
+        <v>-5.80561888623029</v>
       </c>
       <c r="O13">
-        <v>-1.317687866593464</v>
+        <v>-1.497849672647415</v>
       </c>
       <c r="P13">
-        <v>-3.789629445784302</v>
+        <v>-4.307769213582875</v>
       </c>
       <c r="Q13">
-        <v>-3.377629445784303</v>
+        <v>-3.895769213582875</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07119589396334335</v>
+        <v>0.07148448366747225</v>
       </c>
       <c r="T13">
-        <v>0.5865102531949964</v>
+        <v>0.5931751424358487</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.08645548321898826</v>
+        <v>0.07925085961740591</v>
       </c>
       <c r="W13">
-        <v>0.2154137970569626</v>
+        <v>0.2171126473022157</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.3350987721666212</v>
+        <v>0.3071738744860694</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2384,22 +2384,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08895986330364145</v>
+        <v>0.09085986330364146</v>
       </c>
       <c r="C14">
-        <v>67.21881895499453</v>
+        <v>60.331071713513</v>
       </c>
       <c r="D14">
-        <v>93.11579472357083</v>
+        <v>89.18946212947066</v>
       </c>
       <c r="E14">
-        <v>-260.3414889695595</v>
+        <v>-257.3800743221781</v>
       </c>
       <c r="F14">
-        <v>35.53697576857629</v>
+        <v>38.49839041595765</v>
       </c>
       <c r="G14">
         <v>9.640000000000001</v>
@@ -2420,37 +2420,37 @@
         <v>2.574</v>
       </c>
       <c r="M14">
-        <v>8.37961888623029</v>
+        <v>9.077920460082815</v>
       </c>
       <c r="N14">
-        <v>-5.80561888623029</v>
+        <v>-6.503920460082815</v>
       </c>
       <c r="O14">
-        <v>-1.497849672647415</v>
+        <v>-1.678011478701366</v>
       </c>
       <c r="P14">
-        <v>-4.307769213582875</v>
+        <v>-4.825908981381449</v>
       </c>
       <c r="Q14">
-        <v>-3.895769213582875</v>
+        <v>-4.413908981381449</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07148448366747225</v>
+        <v>0.07177970761767308</v>
       </c>
       <c r="T14">
-        <v>0.5931751424358487</v>
+        <v>0.5999932475213182</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.07925085961740591</v>
+        <v>0.07315463964683622</v>
       </c>
       <c r="W14">
-        <v>0.2171126473022157</v>
+        <v>0.218550135971276</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3071738744860694</v>
+        <v>0.2835451149102178</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2466,22 +2466,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09085986330364146</v>
+        <v>0.09275986330364147</v>
       </c>
       <c r="C15">
-        <v>60.331071713513</v>
+        <v>53.76104396284661</v>
       </c>
       <c r="D15">
-        <v>89.18946212947066</v>
+        <v>85.58084902618562</v>
       </c>
       <c r="E15">
-        <v>-257.3800743221781</v>
+        <v>-254.4186596747968</v>
       </c>
       <c r="F15">
-        <v>38.49839041595765</v>
+        <v>41.45980506333901</v>
       </c>
       <c r="G15">
         <v>9.640000000000001</v>
@@ -2502,37 +2502,37 @@
         <v>2.574</v>
       </c>
       <c r="M15">
-        <v>9.077920460082815</v>
+        <v>9.776222033935339</v>
       </c>
       <c r="N15">
-        <v>-6.503920460082815</v>
+        <v>-7.202222033935339</v>
       </c>
       <c r="O15">
-        <v>-1.678011478701366</v>
+        <v>-1.858173284755317</v>
       </c>
       <c r="P15">
-        <v>-4.825908981381449</v>
+        <v>-5.344048749180022</v>
       </c>
       <c r="Q15">
-        <v>-4.413908981381449</v>
+        <v>-4.932048749180022</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07177970761767308</v>
+        <v>0.07208179724113439</v>
       </c>
       <c r="T15">
-        <v>0.5999932475213182</v>
+        <v>0.6069699131901708</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.07315463964683622</v>
+        <v>0.06792930824349078</v>
       </c>
       <c r="W15">
-        <v>0.218550135971276</v>
+        <v>0.2197822691161849</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.2835451149102178</v>
+        <v>0.2632918924166309</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2548,22 +2548,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09275986330364147</v>
+        <v>0.09465986330364146</v>
       </c>
       <c r="C16">
-        <v>53.76104396284661</v>
+        <v>47.47167049291911</v>
       </c>
       <c r="D16">
-        <v>85.58084902618562</v>
+        <v>82.25289020363948</v>
       </c>
       <c r="E16">
-        <v>-254.4186596747968</v>
+        <v>-251.4572450274154</v>
       </c>
       <c r="F16">
-        <v>41.45980506333901</v>
+        <v>44.42121971072037</v>
       </c>
       <c r="G16">
         <v>9.640000000000001</v>
@@ -2584,37 +2584,37 @@
         <v>2.574</v>
       </c>
       <c r="M16">
-        <v>9.776222033935339</v>
+        <v>10.47452360778786</v>
       </c>
       <c r="N16">
-        <v>-7.202222033935339</v>
+        <v>-7.900523607787864</v>
       </c>
       <c r="O16">
-        <v>-1.858173284755317</v>
+        <v>-2.038335090809269</v>
       </c>
       <c r="P16">
-        <v>-5.344048749180022</v>
+        <v>-5.862188516978595</v>
       </c>
       <c r="Q16">
-        <v>-4.932048749180022</v>
+        <v>-5.450188516978595</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07208179724113439</v>
+        <v>0.07239099485573597</v>
       </c>
       <c r="T16">
-        <v>0.6069699131901708</v>
+        <v>0.6141107356982904</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.06792930824349078</v>
+        <v>0.06340068769392472</v>
       </c>
       <c r="W16">
-        <v>0.2197822691161849</v>
+        <v>0.2208501178417726</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.2632918924166309</v>
+        <v>0.2457390995888555</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2630,22 +2630,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09465986330364146</v>
+        <v>0.09655986330364147</v>
       </c>
       <c r="C17">
-        <v>47.47167049291912</v>
+        <v>41.43143566723941</v>
       </c>
       <c r="D17">
-        <v>82.25289020363948</v>
+        <v>79.17407002534114</v>
       </c>
       <c r="E17">
-        <v>-251.4572450274154</v>
+        <v>-248.4958303800341</v>
       </c>
       <c r="F17">
-        <v>44.42121971072037</v>
+        <v>47.38263435810173</v>
       </c>
       <c r="G17">
         <v>9.640000000000001</v>
@@ -2666,37 +2666,37 @@
         <v>2.574</v>
       </c>
       <c r="M17">
-        <v>10.47452360778786</v>
+        <v>11.17282518164039</v>
       </c>
       <c r="N17">
-        <v>-7.900523607787862</v>
+        <v>-8.598825181640388</v>
       </c>
       <c r="O17">
-        <v>-2.038335090809269</v>
+        <v>-2.21849689686322</v>
       </c>
       <c r="P17">
-        <v>-5.862188516978594</v>
+        <v>-6.380328284777168</v>
       </c>
       <c r="Q17">
-        <v>-5.450188516978594</v>
+        <v>-5.968328284777168</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07239099485573597</v>
+        <v>0.07270755431830427</v>
       </c>
       <c r="T17">
-        <v>0.6141107356982904</v>
+        <v>0.6214215777899368</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.06340068769392473</v>
+        <v>0.05943814471305443</v>
       </c>
       <c r="W17">
-        <v>0.2208501178417726</v>
+        <v>0.2217844854766618</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.2457390995888555</v>
+        <v>0.230380405864552</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2712,22 +2712,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09655986330364147</v>
+        <v>0.09845986330364148</v>
       </c>
       <c r="C18">
-        <v>41.43143566723941</v>
+        <v>35.61337226289582</v>
       </c>
       <c r="D18">
-        <v>79.17407002534114</v>
+        <v>76.31742126837891</v>
       </c>
       <c r="E18">
-        <v>-248.4958303800341</v>
+        <v>-245.5344157326527</v>
       </c>
       <c r="F18">
-        <v>47.38263435810173</v>
+        <v>50.34404900548309</v>
       </c>
       <c r="G18">
         <v>9.640000000000001</v>
@@ -2748,37 +2748,37 @@
         <v>2.574</v>
       </c>
       <c r="M18">
-        <v>11.17282518164039</v>
+        <v>11.87112675549291</v>
       </c>
       <c r="N18">
-        <v>-8.598825181640388</v>
+        <v>-9.297126755492913</v>
       </c>
       <c r="O18">
-        <v>-2.21849689686322</v>
+        <v>-2.398658702917172</v>
       </c>
       <c r="P18">
-        <v>-6.380328284777168</v>
+        <v>-6.898468052575741</v>
       </c>
       <c r="Q18">
-        <v>-5.968328284777168</v>
+        <v>-6.486468052575741</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07270755431830427</v>
+        <v>0.07303174171972962</v>
       </c>
       <c r="T18">
-        <v>0.6214215777899368</v>
+        <v>0.6289085847512613</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.05943814471305443</v>
+        <v>0.05594178325934534</v>
       </c>
       <c r="W18">
-        <v>0.2217844854766618</v>
+        <v>0.2226089275074464</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.230380405864552</v>
+        <v>0.2168286172842843</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2794,22 +2794,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09845986330364148</v>
+        <v>0.1003598633036415</v>
       </c>
       <c r="C19">
-        <v>35.61337226289582</v>
+        <v>29.99426949773208</v>
       </c>
       <c r="D19">
-        <v>76.31742126837891</v>
+        <v>73.65973315059652</v>
       </c>
       <c r="E19">
-        <v>-245.5344157326527</v>
+        <v>-242.5730010852714</v>
       </c>
       <c r="F19">
-        <v>50.34404900548309</v>
+        <v>53.30546365286445</v>
       </c>
       <c r="G19">
         <v>9.640000000000001</v>
@@ -2830,37 +2830,37 @@
         <v>2.574</v>
       </c>
       <c r="M19">
-        <v>11.87112675549291</v>
+        <v>12.56942832934544</v>
       </c>
       <c r="N19">
-        <v>-9.297126755492913</v>
+        <v>-9.995428329345437</v>
       </c>
       <c r="O19">
-        <v>-2.398658702917172</v>
+        <v>-2.578820508971123</v>
       </c>
       <c r="P19">
-        <v>-6.898468052575741</v>
+        <v>-7.416607820374313</v>
       </c>
       <c r="Q19">
-        <v>-6.486468052575741</v>
+        <v>-7.004607820374313</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07303174171972962</v>
+        <v>0.07336383613094583</v>
       </c>
       <c r="T19">
-        <v>0.6289085847512613</v>
+        <v>0.6365782016384718</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.05594178325934534</v>
+        <v>0.05283390641160393</v>
       </c>
       <c r="W19">
-        <v>0.2226089275074464</v>
+        <v>0.2233417648681438</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.2168286172842843</v>
+        <v>0.2047825829907129</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2876,22 +2876,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1003598633036415</v>
+        <v>0.1022598633036415</v>
       </c>
       <c r="C20">
-        <v>29.99426949773208</v>
+        <v>24.55404096740769</v>
       </c>
       <c r="D20">
-        <v>73.65973315059652</v>
+        <v>71.18091926765348</v>
       </c>
       <c r="E20">
-        <v>-242.5730010852714</v>
+        <v>-239.61158643789</v>
       </c>
       <c r="F20">
-        <v>53.30546365286444</v>
+        <v>56.26687830024579</v>
       </c>
       <c r="G20">
         <v>9.640000000000001</v>
@@ -2912,37 +2912,37 @@
         <v>2.574</v>
       </c>
       <c r="M20">
-        <v>12.56942832934543</v>
+        <v>13.26772990319796</v>
       </c>
       <c r="N20">
-        <v>-9.995428329345435</v>
+        <v>-10.69372990319796</v>
       </c>
       <c r="O20">
-        <v>-2.578820508971122</v>
+        <v>-2.758982315025073</v>
       </c>
       <c r="P20">
-        <v>-7.416607820374312</v>
+        <v>-7.934747588172885</v>
       </c>
       <c r="Q20">
-        <v>-7.004607820374313</v>
+        <v>-7.522747588172885</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07336383613094583</v>
+        <v>0.07370413040416739</v>
       </c>
       <c r="T20">
-        <v>0.6365782016384717</v>
+        <v>0.6444371917821566</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.05283390641160394</v>
+        <v>0.05005317449520373</v>
       </c>
       <c r="W20">
-        <v>0.2233417648681438</v>
+        <v>0.223997461454031</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2047825829907129</v>
+        <v>0.1940045523069912</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2958,22 +2958,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1022598633036415</v>
+        <v>0.1041598633036415</v>
       </c>
       <c r="C21">
-        <v>24.55404096740769</v>
+        <v>19.27521604946283</v>
       </c>
       <c r="D21">
-        <v>71.18091926765348</v>
+        <v>68.86350899708998</v>
       </c>
       <c r="E21">
-        <v>-239.61158643789</v>
+        <v>-236.6501717905086</v>
       </c>
       <c r="F21">
-        <v>56.26687830024579</v>
+        <v>59.22829294762715</v>
       </c>
       <c r="G21">
         <v>9.640000000000001</v>
@@ -2994,37 +2994,37 @@
         <v>2.574</v>
       </c>
       <c r="M21">
-        <v>13.26772990319796</v>
+        <v>13.96603147705048</v>
       </c>
       <c r="N21">
-        <v>-10.69372990319796</v>
+        <v>-11.39203147705048</v>
       </c>
       <c r="O21">
-        <v>-2.758982315025073</v>
+        <v>-2.939144121079025</v>
       </c>
       <c r="P21">
-        <v>-7.934747588172885</v>
+        <v>-8.452887355971459</v>
       </c>
       <c r="Q21">
-        <v>-7.522747588172885</v>
+        <v>-8.04088735597146</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07370413040416739</v>
+        <v>0.07405293203421948</v>
       </c>
       <c r="T21">
-        <v>0.6444371917821566</v>
+        <v>0.6524926566794336</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.05005317449520373</v>
+        <v>0.04755051577044355</v>
       </c>
       <c r="W21">
-        <v>0.223997461454031</v>
+        <v>0.2245875883813294</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.1940045523069912</v>
+        <v>0.1843043246916416</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3040,22 +3040,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1041598633036415</v>
+        <v>0.1060598633036415</v>
       </c>
       <c r="C22">
-        <v>19.27521604946283</v>
+        <v>14.14252752389187</v>
       </c>
       <c r="D22">
-        <v>68.86350899708998</v>
+        <v>66.69223511890038</v>
       </c>
       <c r="E22">
-        <v>-236.6501717905086</v>
+        <v>-233.6887571431273</v>
       </c>
       <c r="F22">
-        <v>59.22829294762715</v>
+        <v>62.18970759500851</v>
       </c>
       <c r="G22">
         <v>9.640000000000001</v>
@@ -3076,37 +3076,37 @@
         <v>2.574</v>
       </c>
       <c r="M22">
-        <v>13.96603147705048</v>
+        <v>14.66433305090301</v>
       </c>
       <c r="N22">
-        <v>-11.39203147705048</v>
+        <v>-12.09033305090301</v>
       </c>
       <c r="O22">
-        <v>-2.939144121079025</v>
+        <v>-3.119305927132976</v>
       </c>
       <c r="P22">
-        <v>-8.452887355971459</v>
+        <v>-8.971027123770032</v>
       </c>
       <c r="Q22">
-        <v>-8.04088735597146</v>
+        <v>-8.559027123770033</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07405293203421948</v>
+        <v>0.07441056408528554</v>
       </c>
       <c r="T22">
-        <v>0.6524926566794336</v>
+        <v>0.6607520573968947</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.04755051577044355</v>
+        <v>0.04528620549566052</v>
       </c>
       <c r="W22">
-        <v>0.2245875883813294</v>
+        <v>0.2251215127441233</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1843043246916416</v>
+        <v>0.175527928277754</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3122,22 +3122,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1060598633036414</v>
+        <v>0.1079598633036415</v>
       </c>
       <c r="C23">
-        <v>14.14252752389192</v>
+        <v>9.142574823314902</v>
       </c>
       <c r="D23">
-        <v>66.69223511890043</v>
+        <v>64.65369706570478</v>
       </c>
       <c r="E23">
-        <v>-233.6887571431273</v>
+        <v>-230.7273424957459</v>
       </c>
       <c r="F23">
-        <v>62.18970759500851</v>
+        <v>65.15112224238987</v>
       </c>
       <c r="G23">
         <v>9.640000000000001</v>
@@ -3158,37 +3158,37 @@
         <v>2.574</v>
       </c>
       <c r="M23">
-        <v>14.66433305090301</v>
+        <v>15.36263462475553</v>
       </c>
       <c r="N23">
-        <v>-12.09033305090301</v>
+        <v>-12.78863462475553</v>
       </c>
       <c r="O23">
-        <v>-3.119305927132976</v>
+        <v>-3.299467733186928</v>
       </c>
       <c r="P23">
-        <v>-8.971027123770032</v>
+        <v>-9.489166891568605</v>
       </c>
       <c r="Q23">
-        <v>-8.559027123770033</v>
+        <v>-9.077166891568606</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07441056408528554</v>
+        <v>0.07477736618894305</v>
       </c>
       <c r="T23">
-        <v>0.6607520573968947</v>
+        <v>0.6692232376199319</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.04528620549566052</v>
+        <v>0.04322774160949413</v>
       </c>
       <c r="W23">
-        <v>0.2251215127441233</v>
+        <v>0.2256068985284813</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.175527928277754</v>
+        <v>0.1675493860833106</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3204,22 +3204,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1079598633036415</v>
+        <v>0.1098598633036415</v>
       </c>
       <c r="C24">
-        <v>9.142574823314902</v>
+        <v>4.263547210658061</v>
       </c>
       <c r="D24">
-        <v>64.65369706570478</v>
+        <v>62.7360841004293</v>
       </c>
       <c r="E24">
-        <v>-230.7273424957459</v>
+        <v>-227.7659278483646</v>
       </c>
       <c r="F24">
-        <v>65.15112224238987</v>
+        <v>68.11253688977123</v>
       </c>
       <c r="G24">
         <v>9.640000000000001</v>
@@ -3240,37 +3240,37 @@
         <v>2.574</v>
       </c>
       <c r="M24">
-        <v>15.36263462475553</v>
+        <v>16.06093619860806</v>
       </c>
       <c r="N24">
-        <v>-12.78863462475553</v>
+        <v>-13.48693619860806</v>
       </c>
       <c r="O24">
-        <v>-3.299467733186928</v>
+        <v>-3.479629539240879</v>
       </c>
       <c r="P24">
-        <v>-9.489166891568605</v>
+        <v>-10.00730665936718</v>
       </c>
       <c r="Q24">
-        <v>-9.077166891568606</v>
+        <v>-9.595306659367179</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07477736618894305</v>
+        <v>0.07515369561996828</v>
       </c>
       <c r="T24">
-        <v>0.6692232376199319</v>
+        <v>0.6779144484981127</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04322774160949413</v>
+        <v>0.04134827458299438</v>
       </c>
       <c r="W24">
-        <v>0.2256068985284813</v>
+        <v>0.2260500768533299</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1675493860833106</v>
+        <v>0.1602646301666449</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3286,22 +3286,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1098598633036415</v>
+        <v>0.1117598633036415</v>
       </c>
       <c r="C25">
-        <v>4.263547210658061</v>
+        <v>-0.5050051993061686</v>
       </c>
       <c r="D25">
-        <v>62.7360841004293</v>
+        <v>60.92894633784643</v>
       </c>
       <c r="E25">
-        <v>-227.7659278483646</v>
+        <v>-224.8045132009832</v>
       </c>
       <c r="F25">
-        <v>68.11253688977123</v>
+        <v>71.0739515371526</v>
       </c>
       <c r="G25">
         <v>9.640000000000001</v>
@@ -3322,37 +3322,37 @@
         <v>2.574</v>
       </c>
       <c r="M25">
-        <v>16.06093619860806</v>
+        <v>16.75923777246058</v>
       </c>
       <c r="N25">
-        <v>-13.48693619860806</v>
+        <v>-14.18523777246058</v>
       </c>
       <c r="O25">
-        <v>-3.479629539240879</v>
+        <v>-3.659791345294831</v>
       </c>
       <c r="P25">
-        <v>-10.00730665936718</v>
+        <v>-10.52544642716575</v>
       </c>
       <c r="Q25">
-        <v>-9.595306659367179</v>
+        <v>-10.11344642716575</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07515369561996828</v>
+        <v>0.07553992845707314</v>
       </c>
       <c r="T25">
-        <v>0.6779144484981127</v>
+        <v>0.6868343754520353</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04134827458299438</v>
+        <v>0.03962542980870295</v>
       </c>
       <c r="W25">
-        <v>0.2260500768533299</v>
+        <v>0.2264563236511078</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1602646301666449</v>
+        <v>0.1535869372430346</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3368,22 +3368,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1117598633036415</v>
+        <v>0.1136598633036415</v>
       </c>
       <c r="C26">
-        <v>-0.5050051993061828</v>
+        <v>-5.172361951579674</v>
       </c>
       <c r="D26">
-        <v>60.92894633784639</v>
+        <v>59.22300423295427</v>
       </c>
       <c r="E26">
-        <v>-224.8045132009832</v>
+        <v>-221.8430985536019</v>
       </c>
       <c r="F26">
-        <v>71.07395153715258</v>
+        <v>74.03536618453394</v>
       </c>
       <c r="G26">
         <v>9.640000000000001</v>
@@ -3404,37 +3404,37 @@
         <v>2.574</v>
       </c>
       <c r="M26">
-        <v>16.75923777246058</v>
+        <v>17.4575393463131</v>
       </c>
       <c r="N26">
-        <v>-14.18523777246058</v>
+        <v>-14.88353934631311</v>
       </c>
       <c r="O26">
-        <v>-3.65979134529483</v>
+        <v>-3.839953151348781</v>
       </c>
       <c r="P26">
-        <v>-10.52544642716575</v>
+        <v>-11.04358619496432</v>
       </c>
       <c r="Q26">
-        <v>-10.11344642716575</v>
+        <v>-10.63158619496432</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07553992845707314</v>
+        <v>0.07593646083650077</v>
       </c>
       <c r="T26">
-        <v>0.6868343754520353</v>
+        <v>0.6959921671247291</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.03962542980870296</v>
+        <v>0.03804041261635483</v>
       </c>
       <c r="W26">
-        <v>0.2264563236511078</v>
+        <v>0.2268300707050635</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1535869372430347</v>
+        <v>0.1474434597533133</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3450,22 +3450,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1136598633036415</v>
+        <v>0.1155598633036415</v>
       </c>
       <c r="C27">
-        <v>-5.172361951579674</v>
+        <v>-9.746791629578823</v>
       </c>
       <c r="D27">
-        <v>59.22300423295427</v>
+        <v>57.60998920233648</v>
       </c>
       <c r="E27">
-        <v>-221.8430985536019</v>
+        <v>-218.8816839062205</v>
       </c>
       <c r="F27">
-        <v>74.03536618453394</v>
+        <v>76.9967808319153</v>
       </c>
       <c r="G27">
         <v>9.640000000000001</v>
@@ -3486,37 +3486,37 @@
         <v>2.574</v>
       </c>
       <c r="M27">
-        <v>17.4575393463131</v>
+        <v>18.15584092016563</v>
       </c>
       <c r="N27">
-        <v>-14.88353934631311</v>
+        <v>-15.58184092016563</v>
       </c>
       <c r="O27">
-        <v>-3.839953151348781</v>
+        <v>-4.020114957402733</v>
       </c>
       <c r="P27">
-        <v>-11.04358619496432</v>
+        <v>-11.5617259627629</v>
       </c>
       <c r="Q27">
-        <v>-10.63158619496432</v>
+        <v>-11.1497259627629</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07593646083650077</v>
+        <v>0.07634371030726429</v>
       </c>
       <c r="T27">
-        <v>0.6959921671247291</v>
+        <v>0.7053974666804688</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.03804041261635483</v>
+        <v>0.03657731982341811</v>
       </c>
       <c r="W27">
-        <v>0.2268300707050635</v>
+        <v>0.227175067985638</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1474434597533133</v>
+        <v>0.141772557455109</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3532,22 +3532,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1155598633036415</v>
+        <v>0.1174598633036415</v>
       </c>
       <c r="C28">
-        <v>-9.746791629578823</v>
+        <v>-14.23568587904417</v>
       </c>
       <c r="D28">
-        <v>57.60998920233648</v>
+        <v>56.08250960025249</v>
       </c>
       <c r="E28">
-        <v>-218.8816839062205</v>
+        <v>-215.9202692588391</v>
       </c>
       <c r="F28">
-        <v>76.9967808319153</v>
+        <v>79.95819547929666</v>
       </c>
       <c r="G28">
         <v>9.640000000000001</v>
@@ -3568,37 +3568,37 @@
         <v>2.574</v>
       </c>
       <c r="M28">
-        <v>18.15584092016563</v>
+        <v>18.85414249401815</v>
       </c>
       <c r="N28">
-        <v>-15.58184092016563</v>
+        <v>-16.28014249401815</v>
       </c>
       <c r="O28">
-        <v>-4.020114957402733</v>
+        <v>-4.200276763456683</v>
       </c>
       <c r="P28">
-        <v>-11.5617259627629</v>
+        <v>-12.07986573056147</v>
       </c>
       <c r="Q28">
-        <v>-11.1497259627629</v>
+        <v>-11.66786573056147</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07634371030726429</v>
+        <v>0.07676211729777477</v>
       </c>
       <c r="T28">
-        <v>0.7053974666804688</v>
+        <v>0.7150604456760916</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.03657731982341811</v>
+        <v>0.03522260427440263</v>
       </c>
       <c r="W28">
-        <v>0.227175067985638</v>
+        <v>0.2274945099120959</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.141772557455109</v>
+        <v>0.1365217219938087</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3614,22 +3614,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1174598633036415</v>
+        <v>0.1193598633036415</v>
       </c>
       <c r="C29">
-        <v>-14.23568587904417</v>
+        <v>-18.64567266148556</v>
       </c>
       <c r="D29">
-        <v>56.08250960025249</v>
+        <v>54.63393746519246</v>
       </c>
       <c r="E29">
-        <v>-215.9202692588391</v>
+        <v>-212.9588546114578</v>
       </c>
       <c r="F29">
-        <v>79.95819547929666</v>
+        <v>82.91961012667802</v>
       </c>
       <c r="G29">
         <v>9.640000000000001</v>
@@ -3650,37 +3650,37 @@
         <v>2.574</v>
       </c>
       <c r="M29">
-        <v>18.85414249401815</v>
+        <v>19.55244406787068</v>
       </c>
       <c r="N29">
-        <v>-16.28014249401815</v>
+        <v>-16.97844406787068</v>
       </c>
       <c r="O29">
-        <v>-4.200276763456683</v>
+        <v>-4.380438569510635</v>
       </c>
       <c r="P29">
-        <v>-12.07986573056147</v>
+        <v>-12.59800549836004</v>
       </c>
       <c r="Q29">
-        <v>-11.66786573056147</v>
+        <v>-12.18600549836004</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07676211729777477</v>
+        <v>0.0771921467046883</v>
       </c>
       <c r="T29">
-        <v>0.7150604456760916</v>
+        <v>0.7249918407549263</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03522260427440263</v>
+        <v>0.03396465412174539</v>
       </c>
       <c r="W29">
-        <v>0.2274945099120959</v>
+        <v>0.2277911345580924</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1365217219938087</v>
+        <v>0.1316459462083156</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3696,22 +3696,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1193598633036415</v>
+        <v>0.1212598633036415</v>
       </c>
       <c r="C30">
-        <v>-18.64567266148556</v>
+        <v>-22.98271239801091</v>
       </c>
       <c r="D30">
-        <v>54.63393746519246</v>
+        <v>53.25831237604847</v>
       </c>
       <c r="E30">
-        <v>-212.9588546114578</v>
+        <v>-209.9974399640764</v>
       </c>
       <c r="F30">
-        <v>82.91961012667802</v>
+        <v>85.88102477405938</v>
       </c>
       <c r="G30">
         <v>9.640000000000001</v>
@@ -3732,37 +3732,37 @@
         <v>2.574</v>
       </c>
       <c r="M30">
-        <v>19.55244406787068</v>
+        <v>20.2507456417232</v>
       </c>
       <c r="N30">
-        <v>-16.97844406787068</v>
+        <v>-17.6767456417232</v>
       </c>
       <c r="O30">
-        <v>-4.380438569510635</v>
+        <v>-4.560600375564586</v>
       </c>
       <c r="P30">
-        <v>-12.59800549836004</v>
+        <v>-13.11614526615861</v>
       </c>
       <c r="Q30">
-        <v>-12.18600549836004</v>
+        <v>-12.70414526615862</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0771921467046883</v>
+        <v>0.07763428961602195</v>
       </c>
       <c r="T30">
-        <v>0.7249918407549263</v>
+        <v>0.7352029934416153</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03396465412174539</v>
+        <v>0.03279345915203003</v>
       </c>
       <c r="W30">
-        <v>0.2277911345580924</v>
+        <v>0.2280673023319513</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1316459462083156</v>
+        <v>0.1271064308218219</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3778,22 +3778,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1212598633036415</v>
+        <v>0.1231598633036415</v>
       </c>
       <c r="C31">
-        <v>-22.98271239801092</v>
+        <v>-27.25217994508926</v>
       </c>
       <c r="D31">
-        <v>53.25831237604844</v>
+        <v>51.95025947635147</v>
       </c>
       <c r="E31">
-        <v>-209.9974399640764</v>
+        <v>-207.0360253166951</v>
       </c>
       <c r="F31">
-        <v>85.88102477405937</v>
+        <v>88.84243942144073</v>
       </c>
       <c r="G31">
         <v>9.640000000000001</v>
@@ -3814,37 +3814,37 @@
         <v>2.574</v>
       </c>
       <c r="M31">
-        <v>20.2507456417232</v>
+        <v>20.94904721557572</v>
       </c>
       <c r="N31">
-        <v>-17.6767456417232</v>
+        <v>-18.37504721557573</v>
       </c>
       <c r="O31">
-        <v>-4.560600375564586</v>
+        <v>-4.740762181618537</v>
       </c>
       <c r="P31">
-        <v>-13.11614526615861</v>
+        <v>-13.63428503395719</v>
       </c>
       <c r="Q31">
-        <v>-12.70414526615862</v>
+        <v>-13.22228503395719</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07763428961602195</v>
+        <v>0.07808906518196512</v>
       </c>
       <c r="T31">
-        <v>0.7352029934416153</v>
+        <v>0.7457058933479241</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03279345915203003</v>
+        <v>0.03170034384696237</v>
       </c>
       <c r="W31">
-        <v>0.2280673023319513</v>
+        <v>0.2283250589208863</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1271064308218217</v>
+        <v>0.1228695497944277</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3860,22 +3860,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1231598633036415</v>
+        <v>0.1250598633036415</v>
       </c>
       <c r="C32">
-        <v>-27.25217994508926</v>
+        <v>-31.45893477968404</v>
       </c>
       <c r="D32">
-        <v>51.95025947635147</v>
+        <v>50.70491928913805</v>
       </c>
       <c r="E32">
-        <v>-207.0360253166951</v>
+        <v>-204.0746106693137</v>
       </c>
       <c r="F32">
-        <v>88.84243942144073</v>
+        <v>91.80385406882209</v>
       </c>
       <c r="G32">
         <v>9.640000000000001</v>
@@ -3896,37 +3896,37 @@
         <v>2.574</v>
       </c>
       <c r="M32">
-        <v>20.94904721557572</v>
+        <v>21.64734878942825</v>
       </c>
       <c r="N32">
-        <v>-18.37504721557573</v>
+        <v>-19.07334878942825</v>
       </c>
       <c r="O32">
-        <v>-4.740762181618537</v>
+        <v>-4.920923987672489</v>
       </c>
       <c r="P32">
-        <v>-13.63428503395719</v>
+        <v>-14.15242480175576</v>
       </c>
       <c r="Q32">
-        <v>-13.22228503395719</v>
+        <v>-13.74042480175576</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07808906518196512</v>
+        <v>0.0785570226483704</v>
       </c>
       <c r="T32">
-        <v>0.7457058933479241</v>
+        <v>0.7565132251355752</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03170034384696237</v>
+        <v>0.03067775210996358</v>
       </c>
       <c r="W32">
-        <v>0.2283250589208863</v>
+        <v>0.2285661860524706</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1228695497944277</v>
+        <v>0.1189060159300913</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3942,22 +3942,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1250598633036415</v>
+        <v>0.1269598633036415</v>
       </c>
       <c r="C33">
-        <v>-31.45893477968404</v>
+        <v>-35.60738132593552</v>
       </c>
       <c r="D33">
-        <v>50.70491928913805</v>
+        <v>49.51788739026793</v>
       </c>
       <c r="E33">
-        <v>-204.0746106693137</v>
+        <v>-201.1131960219323</v>
       </c>
       <c r="F33">
-        <v>91.80385406882209</v>
+        <v>94.76526871620345</v>
       </c>
       <c r="G33">
         <v>9.640000000000001</v>
@@ -3978,37 +3978,37 @@
         <v>2.574</v>
       </c>
       <c r="M33">
-        <v>21.64734878942825</v>
+        <v>22.34565036328078</v>
       </c>
       <c r="N33">
-        <v>-19.07334878942825</v>
+        <v>-19.77165036328078</v>
       </c>
       <c r="O33">
-        <v>-4.920923987672489</v>
+        <v>-5.10108579372644</v>
       </c>
       <c r="P33">
-        <v>-14.15242480175576</v>
+        <v>-14.67056456955434</v>
       </c>
       <c r="Q33">
-        <v>-13.74042480175576</v>
+        <v>-14.25856456955434</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0785570226483704</v>
+        <v>0.07903874356966997</v>
       </c>
       <c r="T33">
-        <v>0.7565132251355752</v>
+        <v>0.7676384196228629</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03067775210996358</v>
+        <v>0.02971907235652722</v>
       </c>
       <c r="W33">
-        <v>0.2285661860524706</v>
+        <v>0.2287922427383309</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1189060159300913</v>
+        <v>0.1151902029322759</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4024,22 +4024,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1269598633036415</v>
+        <v>0.1288598633036415</v>
       </c>
       <c r="C34">
-        <v>-35.60738132593552</v>
+        <v>-39.70152100198165</v>
       </c>
       <c r="D34">
-        <v>49.51788739026793</v>
+        <v>48.38516236160316</v>
       </c>
       <c r="E34">
-        <v>-201.1131960219323</v>
+        <v>-198.151781374551</v>
       </c>
       <c r="F34">
-        <v>94.76526871620345</v>
+        <v>97.72668336358481</v>
       </c>
       <c r="G34">
         <v>9.640000000000001</v>
@@ -4060,37 +4060,37 @@
         <v>2.574</v>
       </c>
       <c r="M34">
-        <v>22.34565036328078</v>
+        <v>23.0439519371333</v>
       </c>
       <c r="N34">
-        <v>-19.77165036328078</v>
+        <v>-20.4699519371333</v>
       </c>
       <c r="O34">
-        <v>-5.10108579372644</v>
+        <v>-5.281247599780392</v>
       </c>
       <c r="P34">
-        <v>-14.67056456955434</v>
+        <v>-15.18870433735291</v>
       </c>
       <c r="Q34">
-        <v>-14.25856456955434</v>
+        <v>-14.77670433735291</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07903874356966997</v>
+        <v>0.07953484421996355</v>
       </c>
       <c r="T34">
-        <v>0.7676384196228629</v>
+        <v>0.7790957094679805</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.02971907235652722</v>
+        <v>0.02881849440632942</v>
       </c>
       <c r="W34">
-        <v>0.2287922427383309</v>
+        <v>0.2290045990189875</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1151902029322759</v>
+        <v>0.1116995907222069</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4106,22 +4106,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1288598633036415</v>
+        <v>0.1307598633036415</v>
       </c>
       <c r="C35">
-        <v>-39.70152100198165</v>
+        <v>-43.74499728308398</v>
       </c>
       <c r="D35">
-        <v>48.38516236160316</v>
+        <v>47.30310072788219</v>
       </c>
       <c r="E35">
-        <v>-198.151781374551</v>
+        <v>-195.1903667271696</v>
       </c>
       <c r="F35">
-        <v>97.72668336358481</v>
+        <v>100.6880980109662</v>
       </c>
       <c r="G35">
         <v>9.640000000000001</v>
@@ -4142,37 +4142,37 @@
         <v>2.574</v>
       </c>
       <c r="M35">
-        <v>23.0439519371333</v>
+        <v>23.74225351098583</v>
       </c>
       <c r="N35">
-        <v>-20.4699519371333</v>
+        <v>-21.16825351098583</v>
       </c>
       <c r="O35">
-        <v>-5.281247599780392</v>
+        <v>-5.461409405834344</v>
       </c>
       <c r="P35">
-        <v>-15.18870433735291</v>
+        <v>-15.70684410515148</v>
       </c>
       <c r="Q35">
-        <v>-14.77670433735291</v>
+        <v>-15.29484410515148</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07953484421996355</v>
+        <v>0.08004597822329633</v>
       </c>
       <c r="T35">
-        <v>0.7790957094679805</v>
+        <v>0.7909001899144649</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.02881849440632942</v>
+        <v>0.02797089162967267</v>
       </c>
       <c r="W35">
-        <v>0.2290045990189875</v>
+        <v>0.2292044637537232</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1116995907222069</v>
+        <v>0.1084143086421421</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4188,22 +4188,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1307598633036415</v>
+        <v>0.1326598633036415</v>
       </c>
       <c r="C36">
-        <v>-43.74499728308398</v>
+        <v>-47.74113485040353</v>
       </c>
       <c r="D36">
-        <v>47.30310072788219</v>
+        <v>46.26837780794401</v>
       </c>
       <c r="E36">
-        <v>-195.1903667271696</v>
+        <v>-192.2289520797883</v>
       </c>
       <c r="F36">
-        <v>100.6880980109662</v>
+        <v>103.6495126583475</v>
       </c>
       <c r="G36">
         <v>9.640000000000001</v>
@@ -4224,37 +4224,37 @@
         <v>2.574</v>
       </c>
       <c r="M36">
-        <v>23.74225351098583</v>
+        <v>24.44055508483835</v>
       </c>
       <c r="N36">
-        <v>-21.16825351098583</v>
+        <v>-21.86655508483835</v>
       </c>
       <c r="O36">
-        <v>-5.461409405834344</v>
+        <v>-5.641571211888293</v>
       </c>
       <c r="P36">
-        <v>-15.70684410515148</v>
+        <v>-16.22498387295005</v>
       </c>
       <c r="Q36">
-        <v>-15.29484410515148</v>
+        <v>-15.81298387295005</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08004597822329633</v>
+        <v>0.08057283942673166</v>
       </c>
       <c r="T36">
-        <v>0.7909001899144649</v>
+        <v>0.8030678851439182</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.02797089162967267</v>
+        <v>0.02717172329739631</v>
       </c>
       <c r="W36">
-        <v>0.2292044637537232</v>
+        <v>0.229392907646474</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1084143086421421</v>
+        <v>0.1053167569666524</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4270,22 +4270,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1326598633036415</v>
+        <v>0.1345598633036415</v>
       </c>
       <c r="C37">
-        <v>-47.74113485040353</v>
+        <v>-51.69297371164786</v>
       </c>
       <c r="D37">
-        <v>46.26837780794401</v>
+        <v>45.27795359408103</v>
       </c>
       <c r="E37">
-        <v>-192.2289520797883</v>
+        <v>-189.2675374324069</v>
       </c>
       <c r="F37">
-        <v>103.6495126583475</v>
+        <v>106.6109273057289</v>
       </c>
       <c r="G37">
         <v>9.640000000000001</v>
@@ -4306,37 +4306,37 @@
         <v>2.574</v>
       </c>
       <c r="M37">
-        <v>24.44055508483835</v>
+        <v>25.13885665869087</v>
       </c>
       <c r="N37">
-        <v>-21.86655508483835</v>
+        <v>-22.56485665869087</v>
       </c>
       <c r="O37">
-        <v>-5.641571211888293</v>
+        <v>-5.821733017942245</v>
       </c>
       <c r="P37">
-        <v>-16.22498387295005</v>
+        <v>-16.74312364074863</v>
       </c>
       <c r="Q37">
-        <v>-15.81298387295005</v>
+        <v>-16.33112364074863</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08057283942673166</v>
+        <v>0.08111616504277434</v>
       </c>
       <c r="T37">
-        <v>0.8030678851439182</v>
+        <v>0.815615820849292</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.02717172329739631</v>
+        <v>0.02641695320580197</v>
       </c>
       <c r="W37">
-        <v>0.229392907646474</v>
+        <v>0.2295708824340719</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1053167569666524</v>
+        <v>0.1023912914953565</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4352,22 +4352,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1345598633036415</v>
+        <v>0.1364598633036415</v>
       </c>
       <c r="C38">
-        <v>-51.69297371164784</v>
+        <v>-55.60329903122628</v>
       </c>
       <c r="D38">
-        <v>45.27795359408103</v>
+        <v>44.32904292188396</v>
       </c>
       <c r="E38">
-        <v>-189.2675374324069</v>
+        <v>-186.3061227850255</v>
       </c>
       <c r="F38">
-        <v>106.6109273057289</v>
+        <v>109.5723419531102</v>
       </c>
       <c r="G38">
         <v>9.640000000000001</v>
@@ -4388,37 +4388,37 @@
         <v>2.574</v>
       </c>
       <c r="M38">
-        <v>25.13885665869087</v>
+        <v>25.83715823254339</v>
       </c>
       <c r="N38">
-        <v>-22.56485665869087</v>
+        <v>-23.2631582325434</v>
       </c>
       <c r="O38">
-        <v>-5.821733017942245</v>
+        <v>-6.001894823996197</v>
       </c>
       <c r="P38">
-        <v>-16.74312364074863</v>
+        <v>-17.2612634085472</v>
       </c>
       <c r="Q38">
-        <v>-16.33112364074863</v>
+        <v>-16.8492634085472</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08111616504277434</v>
+        <v>0.08167673909107234</v>
       </c>
       <c r="T38">
-        <v>0.815615820849292</v>
+        <v>0.8285621037199157</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02641695320580197</v>
+        <v>0.02570298149753705</v>
       </c>
       <c r="W38">
-        <v>0.2295708824340719</v>
+        <v>0.2297392369628808</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1023912914953564</v>
+        <v>0.09962395929277923</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4434,22 +4434,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1364598633036415</v>
+        <v>0.1383598633036415</v>
       </c>
       <c r="C39">
-        <v>-55.60329903122628</v>
+        <v>-59.47466728641797</v>
       </c>
       <c r="D39">
-        <v>44.32904292188396</v>
+        <v>43.41908931407362</v>
       </c>
       <c r="E39">
-        <v>-186.3061227850255</v>
+        <v>-183.3447081376442</v>
       </c>
       <c r="F39">
-        <v>109.5723419531102</v>
+        <v>112.5337566004916</v>
       </c>
       <c r="G39">
         <v>9.640000000000001</v>
@@ -4470,37 +4470,37 @@
         <v>2.574</v>
       </c>
       <c r="M39">
-        <v>25.83715823254339</v>
+        <v>26.53545980639592</v>
       </c>
       <c r="N39">
-        <v>-23.2631582325434</v>
+        <v>-23.96145980639591</v>
       </c>
       <c r="O39">
-        <v>-6.001894823996197</v>
+        <v>-6.182056630050146</v>
       </c>
       <c r="P39">
-        <v>-17.2612634085472</v>
+        <v>-17.77940317634577</v>
       </c>
       <c r="Q39">
-        <v>-16.8492634085472</v>
+        <v>-17.36740317634577</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08167673909107234</v>
+        <v>0.08225539617318642</v>
       </c>
       <c r="T39">
-        <v>0.8285621037199157</v>
+        <v>0.8419260086186239</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02570298149753705</v>
+        <v>0.02502658724760187</v>
       </c>
       <c r="W39">
-        <v>0.2297392369628808</v>
+        <v>0.2298987307270155</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.09962395929277923</v>
+        <v>0.09700227615349566</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4516,22 +4516,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1383598633036415</v>
+        <v>0.1402598633036415</v>
       </c>
       <c r="C40">
-        <v>-59.47466728641797</v>
+        <v>-63.30942926685182</v>
       </c>
       <c r="D40">
-        <v>43.41908931407362</v>
+        <v>42.54574198102113</v>
       </c>
       <c r="E40">
-        <v>-183.3447081376442</v>
+        <v>-180.3832934902628</v>
       </c>
       <c r="F40">
-        <v>112.5337566004916</v>
+        <v>115.4951712478729</v>
       </c>
       <c r="G40">
         <v>9.640000000000001</v>
@@ -4552,37 +4552,37 @@
         <v>2.574</v>
       </c>
       <c r="M40">
-        <v>26.53545980639592</v>
+        <v>27.23376138024844</v>
       </c>
       <c r="N40">
-        <v>-23.96145980639591</v>
+        <v>-24.65976138024844</v>
       </c>
       <c r="O40">
-        <v>-6.182056630050146</v>
+        <v>-6.362218436104098</v>
       </c>
       <c r="P40">
-        <v>-17.77940317634577</v>
+        <v>-18.29754294414434</v>
       </c>
       <c r="Q40">
-        <v>-17.36740317634577</v>
+        <v>-17.88554294414434</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08225539617318642</v>
+        <v>0.08285302561864849</v>
       </c>
       <c r="T40">
-        <v>0.8419260086186239</v>
+        <v>0.8557280743336834</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02502658724760187</v>
+        <v>0.02438487988227874</v>
       </c>
       <c r="W40">
-        <v>0.2298987307270155</v>
+        <v>0.2300500453237587</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.09700227615349566</v>
+        <v>0.09451503830340602</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4598,22 +4598,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1402598633036415</v>
+        <v>0.1421598633036415</v>
       </c>
       <c r="C41">
-        <v>-63.30942926685182</v>
+        <v>-67.10975035299819</v>
       </c>
       <c r="D41">
-        <v>42.54574198102113</v>
+        <v>41.70683554225611</v>
       </c>
       <c r="E41">
-        <v>-180.3832934902628</v>
+        <v>-177.4218788428815</v>
       </c>
       <c r="F41">
-        <v>115.4951712478729</v>
+        <v>118.4565858952543</v>
       </c>
       <c r="G41">
         <v>9.640000000000001</v>
@@ -4634,37 +4634,37 @@
         <v>2.574</v>
       </c>
       <c r="M41">
-        <v>27.23376138024844</v>
+        <v>27.93206295410097</v>
       </c>
       <c r="N41">
-        <v>-24.65976138024844</v>
+        <v>-25.35806295410097</v>
       </c>
       <c r="O41">
-        <v>-6.362218436104098</v>
+        <v>-6.54238024215805</v>
       </c>
       <c r="P41">
-        <v>-18.29754294414434</v>
+        <v>-18.81568271194292</v>
       </c>
       <c r="Q41">
-        <v>-17.88554294414434</v>
+        <v>-18.40368271194292</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08285302561864849</v>
+        <v>0.08347057604562597</v>
       </c>
       <c r="T41">
-        <v>0.8557280743336834</v>
+        <v>0.8699902089059115</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02438487988227874</v>
+        <v>0.02377525788522178</v>
       </c>
       <c r="W41">
-        <v>0.2300500453237587</v>
+        <v>0.2301937941906647</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.09451503830340602</v>
+        <v>0.09215216234582091</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4680,22 +4680,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1421598633036415</v>
+        <v>0.1440598633036415</v>
       </c>
       <c r="C42">
-        <v>-67.10975035299819</v>
+        <v>-70.87762844197226</v>
       </c>
       <c r="D42">
-        <v>41.70683554225611</v>
+        <v>40.9003721006634</v>
       </c>
       <c r="E42">
-        <v>-177.4218788428815</v>
+        <v>-174.4604641955001</v>
       </c>
       <c r="F42">
-        <v>118.4565858952543</v>
+        <v>121.4180005426357</v>
       </c>
       <c r="G42">
         <v>9.640000000000001</v>
@@ -4716,37 +4716,37 @@
         <v>2.574</v>
       </c>
       <c r="M42">
-        <v>27.93206295410097</v>
+        <v>28.63036452795349</v>
       </c>
       <c r="N42">
-        <v>-25.35806295410097</v>
+        <v>-26.05636452795349</v>
       </c>
       <c r="O42">
-        <v>-6.54238024215805</v>
+        <v>-6.722542048212001</v>
       </c>
       <c r="P42">
-        <v>-18.81568271194292</v>
+        <v>-19.33382247974149</v>
       </c>
       <c r="Q42">
-        <v>-18.40368271194292</v>
+        <v>-18.92182247974149</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08347057604562597</v>
+        <v>0.08410906038538234</v>
       </c>
       <c r="T42">
-        <v>0.8699902089059115</v>
+        <v>0.8847358056670286</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02377525788522178</v>
+        <v>0.02319537354655783</v>
       </c>
       <c r="W42">
-        <v>0.2301937941906647</v>
+        <v>0.2303305309177217</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.09215216234582091</v>
+        <v>0.08990454863006914</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4762,22 +4762,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1440598633036415</v>
+        <v>0.1459598633036415</v>
       </c>
       <c r="C43">
-        <v>-70.87762844197226</v>
+        <v>-74.61490983305791</v>
       </c>
       <c r="D43">
-        <v>40.9003721006634</v>
+        <v>40.12450535695913</v>
       </c>
       <c r="E43">
-        <v>-174.4604641955001</v>
+        <v>-171.4990495481188</v>
       </c>
       <c r="F43">
-        <v>121.4180005426357</v>
+        <v>124.379415190017</v>
       </c>
       <c r="G43">
         <v>9.640000000000001</v>
@@ -4798,37 +4798,37 @@
         <v>2.574</v>
       </c>
       <c r="M43">
-        <v>28.63036452795349</v>
+        <v>29.32866610180602</v>
       </c>
       <c r="N43">
-        <v>-26.05636452795349</v>
+        <v>-26.75466610180602</v>
       </c>
       <c r="O43">
-        <v>-6.722542048212001</v>
+        <v>-6.902703854265952</v>
       </c>
       <c r="P43">
-        <v>-19.33382247974149</v>
+        <v>-19.85196224754007</v>
       </c>
       <c r="Q43">
-        <v>-18.92182247974149</v>
+        <v>-19.43996224754007</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08410906038538234</v>
+        <v>0.08476956142650963</v>
       </c>
       <c r="T43">
-        <v>0.8847358056670286</v>
+        <v>0.8999898712819774</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02319537354655783</v>
+        <v>0.02264310274783026</v>
       </c>
       <c r="W43">
-        <v>0.2303305309177217</v>
+        <v>0.2304607563720616</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.08990454863006914</v>
+        <v>0.08776396413887699</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4844,22 +4844,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1459598633036415</v>
+        <v>0.1478598633036415</v>
       </c>
       <c r="C44">
-        <v>-74.61490983305788</v>
+        <v>-78.32330333883149</v>
       </c>
       <c r="D44">
-        <v>40.12450535695913</v>
+        <v>39.37752649856689</v>
       </c>
       <c r="E44">
-        <v>-171.4990495481188</v>
+        <v>-168.5376349007374</v>
       </c>
       <c r="F44">
-        <v>124.379415190017</v>
+        <v>127.3408298373984</v>
       </c>
       <c r="G44">
         <v>9.640000000000001</v>
@@ -4880,37 +4880,37 @@
         <v>2.574</v>
       </c>
       <c r="M44">
-        <v>29.32866610180601</v>
+        <v>30.02696767565854</v>
       </c>
       <c r="N44">
-        <v>-26.75466610180602</v>
+        <v>-27.45296767565853</v>
       </c>
       <c r="O44">
-        <v>-6.902703854265952</v>
+        <v>-7.082865660319902</v>
       </c>
       <c r="P44">
-        <v>-19.85196224754007</v>
+        <v>-20.37010201533863</v>
       </c>
       <c r="Q44">
-        <v>-19.43996224754007</v>
+        <v>-19.95810201533863</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08476956142650961</v>
+        <v>0.08545323794276417</v>
       </c>
       <c r="T44">
-        <v>0.8999898712819773</v>
+        <v>0.9157791672693805</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02264310274783026</v>
+        <v>0.022116518962997</v>
       </c>
       <c r="W44">
-        <v>0.2304607563720616</v>
+        <v>0.2305849248285253</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.08776396413887688</v>
+        <v>0.08572294171704264</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4926,22 +4926,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1478598633036415</v>
+        <v>0.1497598633036415</v>
       </c>
       <c r="C45">
-        <v>-78.32330333883149</v>
+        <v>-82.00439284889285</v>
       </c>
       <c r="D45">
-        <v>39.37752649856689</v>
+        <v>38.6578516358869</v>
       </c>
       <c r="E45">
-        <v>-168.5376349007374</v>
+        <v>-165.576220253356</v>
       </c>
       <c r="F45">
-        <v>127.3408298373984</v>
+        <v>130.3022444847797</v>
       </c>
       <c r="G45">
         <v>9.640000000000001</v>
@@ -4962,37 +4962,37 @@
         <v>2.574</v>
       </c>
       <c r="M45">
-        <v>30.02696767565854</v>
+        <v>30.72526924951107</v>
       </c>
       <c r="N45">
-        <v>-27.45296767565853</v>
+        <v>-28.15126924951107</v>
       </c>
       <c r="O45">
-        <v>-7.082865660319902</v>
+        <v>-7.263027466373855</v>
       </c>
       <c r="P45">
-        <v>-20.37010201533863</v>
+        <v>-20.88824178313721</v>
       </c>
       <c r="Q45">
-        <v>-19.95810201533863</v>
+        <v>-20.47624178313721</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08545323794276417</v>
+        <v>0.08616133147745639</v>
       </c>
       <c r="T45">
-        <v>0.9157791672693805</v>
+        <v>0.9321323666849051</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.022116518962997</v>
+        <v>0.02161387080474706</v>
       </c>
       <c r="W45">
-        <v>0.2305849248285253</v>
+        <v>0.2307034492642406</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.08572294171704264</v>
+        <v>0.08377469304165519</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5008,22 +5008,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1497598633036415</v>
+        <v>0.1516598633036415</v>
       </c>
       <c r="C46">
-        <v>-82.00439284889285</v>
+        <v>-85.65964854061323</v>
       </c>
       <c r="D46">
-        <v>38.6578516358869</v>
+        <v>37.96401059154788</v>
       </c>
       <c r="E46">
-        <v>-165.576220253356</v>
+        <v>-162.6148056059747</v>
       </c>
       <c r="F46">
-        <v>130.3022444847797</v>
+        <v>133.2636591321611</v>
       </c>
       <c r="G46">
         <v>9.640000000000001</v>
@@ -5044,37 +5044,37 @@
         <v>2.574</v>
       </c>
       <c r="M46">
-        <v>30.72526924951107</v>
+        <v>31.42357082336359</v>
       </c>
       <c r="N46">
-        <v>-28.15126924951107</v>
+        <v>-28.84957082336359</v>
       </c>
       <c r="O46">
-        <v>-7.263027466373855</v>
+        <v>-7.443189272427807</v>
       </c>
       <c r="P46">
-        <v>-20.88824178313721</v>
+        <v>-21.40638155093578</v>
       </c>
       <c r="Q46">
-        <v>-20.47624178313721</v>
+        <v>-20.99438155093578</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08616133147745639</v>
+        <v>0.08689517386795559</v>
       </c>
       <c r="T46">
-        <v>0.9321323666849051</v>
+        <v>0.9490802278973578</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02161387080474706</v>
+        <v>0.02113356256464157</v>
       </c>
       <c r="W46">
-        <v>0.2307034492642406</v>
+        <v>0.2308167059472575</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.08377469304165519</v>
+        <v>0.08191303319628507</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5090,22 +5090,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1516598633036415</v>
+        <v>0.1535598633036415</v>
       </c>
       <c r="C47">
-        <v>-85.65964854061323</v>
+        <v>-89.29043690389</v>
       </c>
       <c r="D47">
-        <v>37.96401059154788</v>
+        <v>37.29463687565246</v>
       </c>
       <c r="E47">
-        <v>-162.6148056059747</v>
+        <v>-159.6533909585933</v>
       </c>
       <c r="F47">
-        <v>133.2636591321611</v>
+        <v>136.2250737795425</v>
       </c>
       <c r="G47">
         <v>9.640000000000001</v>
@@ -5126,37 +5126,37 @@
         <v>2.574</v>
       </c>
       <c r="M47">
-        <v>31.42357082336359</v>
+        <v>32.12187239721612</v>
       </c>
       <c r="N47">
-        <v>-28.84957082336359</v>
+        <v>-29.54787239721612</v>
       </c>
       <c r="O47">
-        <v>-7.443189272427807</v>
+        <v>-7.623351078481758</v>
       </c>
       <c r="P47">
-        <v>-21.40638155093578</v>
+        <v>-21.92452131873436</v>
       </c>
       <c r="Q47">
-        <v>-20.99438155093578</v>
+        <v>-21.51252131873436</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08689517386795559</v>
+        <v>0.08765619560625107</v>
       </c>
       <c r="T47">
-        <v>0.9490802278973578</v>
+        <v>0.9666557876732349</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02113356256464157</v>
+        <v>0.02067413729149719</v>
       </c>
       <c r="W47">
-        <v>0.2308167059472575</v>
+        <v>0.230925038426665</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.08191303319628507</v>
+        <v>0.08013231508332241</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5172,22 +5172,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1535598633036415</v>
+        <v>0.1554598633036415</v>
       </c>
       <c r="C48">
-        <v>-89.29043690389</v>
+        <v>-92.8980297237494</v>
       </c>
       <c r="D48">
-        <v>37.29463687565246</v>
+        <v>36.64845870317442</v>
       </c>
       <c r="E48">
-        <v>-159.6533909585933</v>
+        <v>-156.691976311212</v>
       </c>
       <c r="F48">
-        <v>136.2250737795425</v>
+        <v>139.1864884269238</v>
       </c>
       <c r="G48">
         <v>9.640000000000001</v>
@@ -5208,37 +5208,37 @@
         <v>2.574</v>
       </c>
       <c r="M48">
-        <v>32.12187239721612</v>
+        <v>32.82017397106864</v>
       </c>
       <c r="N48">
-        <v>-29.54787239721612</v>
+        <v>-30.24617397106864</v>
       </c>
       <c r="O48">
-        <v>-7.623351078481758</v>
+        <v>-7.80351288453571</v>
       </c>
       <c r="P48">
-        <v>-21.92452131873436</v>
+        <v>-22.44266108653293</v>
       </c>
       <c r="Q48">
-        <v>-21.51252131873436</v>
+        <v>-22.03066108653293</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08765619560625107</v>
+        <v>0.08844593514599165</v>
       </c>
       <c r="T48">
-        <v>0.9666557876732349</v>
+        <v>0.9848945761198996</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02067413729149719</v>
+        <v>0.02023426202997598</v>
       </c>
       <c r="W48">
-        <v>0.230925038426665</v>
+        <v>0.2310287610133317</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.08013231508332241</v>
+        <v>0.07842737220920915</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5254,22 +5254,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1554598633036415</v>
+        <v>0.1573598633036415</v>
       </c>
       <c r="C49">
-        <v>-92.8980297237494</v>
+        <v>-96.48361214504163</v>
       </c>
       <c r="D49">
-        <v>36.64845870317442</v>
+        <v>36.02429092926356</v>
       </c>
       <c r="E49">
-        <v>-156.691976311212</v>
+        <v>-153.7305616638306</v>
       </c>
       <c r="F49">
-        <v>139.1864884269238</v>
+        <v>142.1479030743052</v>
       </c>
       <c r="G49">
         <v>9.640000000000001</v>
@@ -5290,37 +5290,37 @@
         <v>2.574</v>
       </c>
       <c r="M49">
-        <v>32.82017397106864</v>
+        <v>33.51847554492117</v>
       </c>
       <c r="N49">
-        <v>-30.24617397106864</v>
+        <v>-30.94447554492117</v>
       </c>
       <c r="O49">
-        <v>-7.80351288453571</v>
+        <v>-7.983674690589662</v>
       </c>
       <c r="P49">
-        <v>-22.44266108653293</v>
+        <v>-22.96080085433151</v>
       </c>
       <c r="Q49">
-        <v>-22.03066108653293</v>
+        <v>-22.54880085433151</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08844593514599165</v>
+        <v>0.08926604928341457</v>
       </c>
       <c r="T49">
-        <v>0.9848945761198996</v>
+        <v>1.003834856429898</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02023426202997598</v>
+        <v>0.01981271490435147</v>
       </c>
       <c r="W49">
-        <v>0.2310287610133317</v>
+        <v>0.2311281618255539</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.07842737220920915</v>
+        <v>0.07679346862151726</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5336,22 +5336,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1573598633036415</v>
+        <v>0.1592598633036415</v>
       </c>
       <c r="C50">
-        <v>-96.4836121450416</v>
+        <v>-100.0482899268269</v>
       </c>
       <c r="D50">
-        <v>36.02429092926356</v>
+        <v>35.4210277948596</v>
       </c>
       <c r="E50">
-        <v>-153.7305616638306</v>
+        <v>-150.7691470164493</v>
       </c>
       <c r="F50">
-        <v>142.1479030743052</v>
+        <v>145.1093177216865</v>
       </c>
       <c r="G50">
         <v>9.640000000000001</v>
@@ -5372,37 +5372,37 @@
         <v>2.574</v>
       </c>
       <c r="M50">
-        <v>33.51847554492116</v>
+        <v>34.21677711877368</v>
       </c>
       <c r="N50">
-        <v>-30.94447554492116</v>
+        <v>-31.64277711877369</v>
       </c>
       <c r="O50">
-        <v>-7.98367469058966</v>
+        <v>-8.163836496643611</v>
       </c>
       <c r="P50">
-        <v>-22.9608008543315</v>
+        <v>-23.47894062213008</v>
       </c>
       <c r="Q50">
-        <v>-22.5488008543315</v>
+        <v>-23.06694062213008</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08926604928341457</v>
+        <v>0.09011832475955996</v>
       </c>
       <c r="T50">
-        <v>1.003834856429898</v>
+        <v>1.023517892830484</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01981271490435148</v>
+        <v>0.01940837378385451</v>
       </c>
       <c r="W50">
-        <v>0.2311281618255539</v>
+        <v>0.2312235054617671</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.07679346862151726</v>
+        <v>0.07522625497618018</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5418,22 +5418,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1592598633036415</v>
+        <v>0.1611598633036415</v>
       </c>
       <c r="C51">
-        <v>-100.0482899268269</v>
+        <v>-103.593095979875</v>
       </c>
       <c r="D51">
-        <v>35.4210277948596</v>
+        <v>34.83763638919288</v>
       </c>
       <c r="E51">
-        <v>-150.7691470164493</v>
+        <v>-147.8077323690679</v>
       </c>
       <c r="F51">
-        <v>145.1093177216865</v>
+        <v>148.0707323690679</v>
       </c>
       <c r="G51">
         <v>9.640000000000001</v>
@@ -5454,37 +5454,37 @@
         <v>2.574</v>
       </c>
       <c r="M51">
-        <v>34.21677711877368</v>
+        <v>34.91507869262621</v>
       </c>
       <c r="N51">
-        <v>-31.64277711877369</v>
+        <v>-32.34107869262621</v>
       </c>
       <c r="O51">
-        <v>-8.163836496643611</v>
+        <v>-8.343998302697562</v>
       </c>
       <c r="P51">
-        <v>-23.47894062213008</v>
+        <v>-23.99708038992865</v>
       </c>
       <c r="Q51">
-        <v>-23.06694062213008</v>
+        <v>-23.58508038992865</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09011832475955996</v>
+        <v>0.09100469125475116</v>
       </c>
       <c r="T51">
-        <v>1.023517892830484</v>
+        <v>1.043988250687094</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01940837378385451</v>
+        <v>0.01902020630817742</v>
       </c>
       <c r="W51">
-        <v>0.2312235054617671</v>
+        <v>0.2313150353525318</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.07522625497618018</v>
+        <v>0.07372172987665659</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5500,22 +5500,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1611598633036415</v>
+        <v>0.1630598633036415</v>
       </c>
       <c r="C52">
-        <v>-103.593095979875</v>
+        <v>-107.1189962685885</v>
       </c>
       <c r="D52">
-        <v>34.83763638919288</v>
+        <v>34.27315074786079</v>
       </c>
       <c r="E52">
-        <v>-147.8077323690679</v>
+        <v>-144.8463177216865</v>
       </c>
       <c r="F52">
-        <v>148.0707323690679</v>
+        <v>151.0321470164492</v>
       </c>
       <c r="G52">
         <v>9.640000000000001</v>
@@ -5536,37 +5536,37 @@
         <v>2.574</v>
       </c>
       <c r="M52">
-        <v>34.91507869262621</v>
+        <v>35.61338026647874</v>
       </c>
       <c r="N52">
-        <v>-32.34107869262621</v>
+        <v>-33.03938026647874</v>
       </c>
       <c r="O52">
-        <v>-8.343998302697562</v>
+        <v>-8.524160108751515</v>
       </c>
       <c r="P52">
-        <v>-23.99708038992865</v>
+        <v>-24.51522015772722</v>
       </c>
       <c r="Q52">
-        <v>-23.58508038992865</v>
+        <v>-24.10322015772722</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09100469125475116</v>
+        <v>0.09192723597423588</v>
       </c>
       <c r="T52">
-        <v>1.043988250687094</v>
+        <v>1.065294133354177</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01902020630817742</v>
+        <v>0.01864726108644845</v>
       </c>
       <c r="W52">
-        <v>0.2313150353525318</v>
+        <v>0.2314029758358155</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.07372172987665659</v>
+        <v>0.07227620576142801</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5582,22 +5582,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1630598633036415</v>
+        <v>0.1649598633036415</v>
       </c>
       <c r="C53">
-        <v>-107.1189962685885</v>
+        <v>-110.6268951482905</v>
       </c>
       <c r="D53">
-        <v>34.27315074786079</v>
+        <v>33.72666651554007</v>
       </c>
       <c r="E53">
-        <v>-144.8463177216865</v>
+        <v>-141.8849030743052</v>
       </c>
       <c r="F53">
-        <v>151.0321470164492</v>
+        <v>153.9935616638306</v>
       </c>
       <c r="G53">
         <v>9.640000000000001</v>
@@ -5618,37 +5618,37 @@
         <v>2.574</v>
       </c>
       <c r="M53">
-        <v>35.61338026647874</v>
+        <v>36.31168184033126</v>
       </c>
       <c r="N53">
-        <v>-33.03938026647874</v>
+        <v>-33.73768184033126</v>
       </c>
       <c r="O53">
-        <v>-8.524160108751515</v>
+        <v>-8.704321914805465</v>
       </c>
       <c r="P53">
-        <v>-24.51522015772722</v>
+        <v>-25.0333599255258</v>
       </c>
       <c r="Q53">
-        <v>-24.10322015772722</v>
+        <v>-24.6213599255258</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09192723597423588</v>
+        <v>0.09288822005703246</v>
       </c>
       <c r="T53">
-        <v>1.065294133354177</v>
+        <v>1.087487761132389</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01864726108644845</v>
+        <v>0.01828865991170905</v>
       </c>
       <c r="W53">
-        <v>0.2314029758358155</v>
+        <v>0.231487533992819</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.07227620576142801</v>
+        <v>0.07088627872755437</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5664,22 +5664,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1649598633036415</v>
+        <v>0.1668598633036415</v>
       </c>
       <c r="C54">
-        <v>-110.6268951482905</v>
+        <v>-114.11764019991</v>
       </c>
       <c r="D54">
-        <v>33.72666651554007</v>
+        <v>33.19733611130194</v>
       </c>
       <c r="E54">
-        <v>-141.8849030743052</v>
+        <v>-138.9234884269238</v>
       </c>
       <c r="F54">
-        <v>153.9935616638306</v>
+        <v>156.954976311212</v>
       </c>
       <c r="G54">
         <v>9.640000000000001</v>
@@ -5700,37 +5700,37 @@
         <v>2.574</v>
       </c>
       <c r="M54">
-        <v>36.31168184033126</v>
+        <v>37.00998341418379</v>
       </c>
       <c r="N54">
-        <v>-33.73768184033126</v>
+        <v>-34.43598341418379</v>
       </c>
       <c r="O54">
-        <v>-8.704321914805465</v>
+        <v>-8.884483720859418</v>
       </c>
       <c r="P54">
-        <v>-25.0333599255258</v>
+        <v>-25.55149969332437</v>
       </c>
       <c r="Q54">
-        <v>-24.6213599255258</v>
+        <v>-25.13949969332437</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09288822005703246</v>
+        <v>0.09389009707952251</v>
       </c>
       <c r="T54">
-        <v>1.087487761132389</v>
+        <v>1.110625798603291</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01828865991170905</v>
+        <v>0.01794359085677115</v>
       </c>
       <c r="W54">
-        <v>0.231487533992819</v>
+        <v>0.2315689012759734</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.07088627872755437</v>
+        <v>0.06954880177043077</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5746,22 +5746,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1668598633036415</v>
+        <v>0.1687598633036415</v>
       </c>
       <c r="C55">
-        <v>-114.11764019991</v>
+        <v>-117.5920266164264</v>
       </c>
       <c r="D55">
-        <v>33.19733611130194</v>
+        <v>32.68436434216689</v>
       </c>
       <c r="E55">
-        <v>-138.9234884269238</v>
+        <v>-135.9620737795425</v>
       </c>
       <c r="F55">
-        <v>156.954976311212</v>
+        <v>159.9163909585933</v>
       </c>
       <c r="G55">
         <v>9.640000000000001</v>
@@ -5782,37 +5782,37 @@
         <v>2.574</v>
       </c>
       <c r="M55">
-        <v>37.00998341418379</v>
+        <v>37.7082849880363</v>
       </c>
       <c r="N55">
-        <v>-34.43598341418379</v>
+        <v>-35.13428498803631</v>
       </c>
       <c r="O55">
-        <v>-8.884483720859418</v>
+        <v>-9.064645526913367</v>
       </c>
       <c r="P55">
-        <v>-25.55149969332437</v>
+        <v>-26.06963946112294</v>
       </c>
       <c r="Q55">
-        <v>-25.13949969332437</v>
+        <v>-25.65763946112294</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09389009707952251</v>
+        <v>0.09493553397255561</v>
       </c>
       <c r="T55">
-        <v>1.110625798603291</v>
+        <v>1.134769837703363</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01794359085677115</v>
+        <v>0.01761130213720132</v>
       </c>
       <c r="W55">
-        <v>0.2315689012759734</v>
+        <v>0.2316472549560479</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.06954880177043077</v>
+        <v>0.06826086099690432</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5828,22 +5828,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1687598633036415</v>
+        <v>0.1706598633036415</v>
       </c>
       <c r="C56">
-        <v>-117.5920266164264</v>
+        <v>-121.0508011888231</v>
       </c>
       <c r="D56">
-        <v>32.68436434216689</v>
+        <v>32.18700441715161</v>
       </c>
       <c r="E56">
-        <v>-135.9620737795425</v>
+        <v>-133.0006591321611</v>
       </c>
       <c r="F56">
-        <v>159.9163909585933</v>
+        <v>162.8778056059747</v>
       </c>
       <c r="G56">
         <v>9.640000000000001</v>
@@ -5864,37 +5864,37 @@
         <v>2.574</v>
       </c>
       <c r="M56">
-        <v>37.7082849880363</v>
+        <v>38.40658656188883</v>
       </c>
       <c r="N56">
-        <v>-35.13428498803631</v>
+        <v>-35.83258656188883</v>
       </c>
       <c r="O56">
-        <v>-9.064645526913367</v>
+        <v>-9.244807332967319</v>
       </c>
       <c r="P56">
-        <v>-26.06963946112294</v>
+        <v>-26.58777922892151</v>
       </c>
       <c r="Q56">
-        <v>-25.65763946112294</v>
+        <v>-26.17577922892151</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09493553397255561</v>
+        <v>0.0960274347275013</v>
       </c>
       <c r="T56">
-        <v>1.134769837703363</v>
+        <v>1.159986945207882</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01761130213720132</v>
+        <v>0.01729109664379765</v>
       </c>
       <c r="W56">
-        <v>0.2316472549560479</v>
+        <v>0.2317227594113925</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.06826086099690432</v>
+        <v>0.0670197544333242</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5910,22 +5910,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1706598633036415</v>
+        <v>0.1725598633036415</v>
       </c>
       <c r="C57">
-        <v>-121.0508011888231</v>
+        <v>-124.4946659335676</v>
       </c>
       <c r="D57">
-        <v>32.18700441715161</v>
+        <v>31.70455431978841</v>
       </c>
       <c r="E57">
-        <v>-133.0006591321611</v>
+        <v>-130.0392444847797</v>
       </c>
       <c r="F57">
-        <v>162.8778056059747</v>
+        <v>165.839220253356</v>
       </c>
       <c r="G57">
         <v>9.640000000000001</v>
@@ -5946,37 +5946,37 @@
         <v>2.574</v>
       </c>
       <c r="M57">
-        <v>38.40658656188883</v>
+        <v>39.10488813574135</v>
       </c>
       <c r="N57">
-        <v>-35.83258656188883</v>
+        <v>-36.53088813574136</v>
       </c>
       <c r="O57">
-        <v>-9.244807332967319</v>
+        <v>-9.42496913902127</v>
       </c>
       <c r="P57">
-        <v>-26.58777922892151</v>
+        <v>-27.10591899672009</v>
       </c>
       <c r="Q57">
-        <v>-26.17577922892151</v>
+        <v>-26.69391899672009</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.0960274347275013</v>
+        <v>0.09716896733494448</v>
       </c>
       <c r="T57">
-        <v>1.159986945207882</v>
+        <v>1.186350284871697</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01729109664379765</v>
+        <v>0.01698232706087269</v>
       </c>
       <c r="W57">
-        <v>0.2317227594113925</v>
+        <v>0.2317955672790462</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.0670197544333242</v>
+        <v>0.06582297310415763</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5992,22 +5992,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1725598633036415</v>
+        <v>0.1744598633036415</v>
       </c>
       <c r="C58">
-        <v>-124.4946659335676</v>
+        <v>-127.9242813986775</v>
       </c>
       <c r="D58">
-        <v>31.70455431978841</v>
+        <v>31.23635350205993</v>
       </c>
       <c r="E58">
-        <v>-130.0392444847797</v>
+        <v>-127.0778298373984</v>
       </c>
       <c r="F58">
-        <v>165.839220253356</v>
+        <v>168.8006349007374</v>
       </c>
       <c r="G58">
         <v>9.640000000000001</v>
@@ -6028,37 +6028,37 @@
         <v>2.574</v>
       </c>
       <c r="M58">
-        <v>39.10488813574135</v>
+        <v>39.80318970959388</v>
       </c>
       <c r="N58">
-        <v>-36.53088813574136</v>
+        <v>-37.22918970959388</v>
       </c>
       <c r="O58">
-        <v>-9.42496913902127</v>
+        <v>-9.605130945075222</v>
       </c>
       <c r="P58">
-        <v>-27.10591899672009</v>
+        <v>-27.62405876451866</v>
       </c>
       <c r="Q58">
-        <v>-26.69391899672009</v>
+        <v>-27.21205876451866</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09716896733494448</v>
+        <v>0.09836359448226878</v>
       </c>
       <c r="T58">
-        <v>1.186350284871697</v>
+        <v>1.213939826380342</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01698232706087269</v>
+        <v>0.01668439149840124</v>
       </c>
       <c r="W58">
-        <v>0.2317955672790462</v>
+        <v>0.231865820484677</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.06582297310415763</v>
+        <v>0.06466818410233033</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6074,22 +6074,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1744598633036415</v>
+        <v>0.1763598633036415</v>
       </c>
       <c r="C59">
-        <v>-127.9242813986775</v>
+        <v>-131.3402696811115</v>
       </c>
       <c r="D59">
-        <v>31.23635350205993</v>
+        <v>30.78177986700728</v>
       </c>
       <c r="E59">
-        <v>-127.0778298373984</v>
+        <v>-124.116415190017</v>
       </c>
       <c r="F59">
-        <v>168.8006349007374</v>
+        <v>171.7620495481188</v>
       </c>
       <c r="G59">
         <v>9.640000000000001</v>
@@ -6110,37 +6110,37 @@
         <v>2.574</v>
       </c>
       <c r="M59">
-        <v>39.80318970959388</v>
+        <v>40.50149128344641</v>
       </c>
       <c r="N59">
-        <v>-37.22918970959388</v>
+        <v>-37.92749128344641</v>
       </c>
       <c r="O59">
-        <v>-9.605130945075222</v>
+        <v>-9.785292751129173</v>
       </c>
       <c r="P59">
-        <v>-27.62405876451866</v>
+        <v>-28.14219853231723</v>
       </c>
       <c r="Q59">
-        <v>-27.21205876451866</v>
+        <v>-27.73019853231724</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09836359448226878</v>
+        <v>0.09961510863660852</v>
       </c>
       <c r="T59">
-        <v>1.213939826380342</v>
+        <v>1.242843155579874</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01668439149840124</v>
+        <v>0.01639672957601502</v>
       </c>
       <c r="W59">
-        <v>0.231865820484677</v>
+        <v>0.2319336511659757</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.06466818410233033</v>
+        <v>0.06355321541091086</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6156,22 +6156,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1763598633036415</v>
+        <v>0.1782598633036415</v>
       </c>
       <c r="C60">
-        <v>-131.3402696811115</v>
+        <v>-134.7432171844738</v>
       </c>
       <c r="D60">
-        <v>30.78177986700728</v>
+        <v>30.34024701102625</v>
       </c>
       <c r="E60">
-        <v>-124.1164151900171</v>
+        <v>-121.1550005426357</v>
       </c>
       <c r="F60">
-        <v>171.7620495481187</v>
+        <v>174.7234641955001</v>
       </c>
       <c r="G60">
         <v>9.640000000000001</v>
@@ -6192,37 +6192,37 @@
         <v>2.574</v>
       </c>
       <c r="M60">
-        <v>40.5014912834464</v>
+        <v>41.19979285729892</v>
       </c>
       <c r="N60">
-        <v>-37.9274912834464</v>
+        <v>-38.62579285729893</v>
       </c>
       <c r="O60">
-        <v>-9.785292751129171</v>
+        <v>-9.965454557183124</v>
       </c>
       <c r="P60">
-        <v>-28.14219853231723</v>
+        <v>-28.6603383001158</v>
       </c>
       <c r="Q60">
-        <v>-27.73019853231723</v>
+        <v>-28.2483383001158</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.0996151086366085</v>
+        <v>0.1009276722618916</v>
       </c>
       <c r="T60">
-        <v>1.242843155579873</v>
+        <v>1.273156403276943</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01639672957601502</v>
+        <v>0.0161188189052351</v>
       </c>
       <c r="W60">
-        <v>0.2319336511659757</v>
+        <v>0.2319991825021456</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.06355321541091086</v>
+        <v>0.06247604226835302</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6238,22 +6238,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1782598633036415</v>
+        <v>0.1801598633036415</v>
       </c>
       <c r="C61">
-        <v>-134.7432171844738</v>
+        <v>-138.1336771427355</v>
       </c>
       <c r="D61">
-        <v>30.34024701102625</v>
+        <v>29.91120170014594</v>
       </c>
       <c r="E61">
-        <v>-121.1550005426357</v>
+        <v>-118.1935858952543</v>
       </c>
       <c r="F61">
-        <v>174.7234641955001</v>
+        <v>177.6848788428815</v>
       </c>
       <c r="G61">
         <v>9.640000000000001</v>
@@ -6274,37 +6274,37 @@
         <v>2.574</v>
       </c>
       <c r="M61">
-        <v>41.19979285729892</v>
+        <v>41.89809443115145</v>
       </c>
       <c r="N61">
-        <v>-38.62579285729893</v>
+        <v>-39.32409443115145</v>
       </c>
       <c r="O61">
-        <v>-9.965454557183124</v>
+        <v>-10.14561636323707</v>
       </c>
       <c r="P61">
-        <v>-28.6603383001158</v>
+        <v>-29.17847806791438</v>
       </c>
       <c r="Q61">
-        <v>-28.2483383001158</v>
+        <v>-28.76647806791438</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1009276722618916</v>
+        <v>0.1023058640684389</v>
       </c>
       <c r="T61">
-        <v>1.273156403276943</v>
+        <v>1.304985313358867</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0161188189052351</v>
+        <v>0.01585017192348118</v>
       </c>
       <c r="W61">
-        <v>0.2319991825021456</v>
+        <v>0.2320625294604431</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.06247604226835302</v>
+        <v>0.06143477489721383</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6320,22 +6320,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1801598633036415</v>
+        <v>0.1820598633036415</v>
       </c>
       <c r="C62">
-        <v>-138.1336771427355</v>
+        <v>-141.5121719328118</v>
       </c>
       <c r="D62">
-        <v>29.91120170014594</v>
+        <v>29.49412155745097</v>
       </c>
       <c r="E62">
-        <v>-118.1935858952543</v>
+        <v>-115.232171247873</v>
       </c>
       <c r="F62">
-        <v>177.6848788428815</v>
+        <v>180.6462934902628</v>
       </c>
       <c r="G62">
         <v>9.640000000000001</v>
@@ -6356,37 +6356,37 @@
         <v>2.574</v>
       </c>
       <c r="M62">
-        <v>41.89809443115145</v>
+        <v>42.59639600500397</v>
       </c>
       <c r="N62">
-        <v>-39.32409443115145</v>
+        <v>-40.02239600500398</v>
       </c>
       <c r="O62">
-        <v>-10.14561636323707</v>
+        <v>-10.32577816929103</v>
       </c>
       <c r="P62">
-        <v>-29.17847806791438</v>
+        <v>-29.69661783571295</v>
       </c>
       <c r="Q62">
-        <v>-28.76647806791438</v>
+        <v>-29.28461783571295</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1023058640684389</v>
+        <v>0.1037547323778861</v>
       </c>
       <c r="T62">
-        <v>1.304985313358867</v>
+        <v>1.338446475239864</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01585017192348118</v>
+        <v>0.01559033303948969</v>
       </c>
       <c r="W62">
-        <v>0.2320625294604431</v>
+        <v>0.2321237994692883</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.06143477489721383</v>
+        <v>0.06042764743988249</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6402,22 +6402,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1820598633036415</v>
+        <v>0.1839598633036415</v>
       </c>
       <c r="C63">
-        <v>-141.5121719328118</v>
+        <v>-144.8791951963222</v>
       </c>
       <c r="D63">
-        <v>29.49412155745097</v>
+        <v>29.088512941322</v>
       </c>
       <c r="E63">
-        <v>-115.232171247873</v>
+        <v>-112.2707566004916</v>
       </c>
       <c r="F63">
-        <v>180.6462934902628</v>
+        <v>183.6077081376442</v>
       </c>
       <c r="G63">
         <v>9.640000000000001</v>
@@ -6438,37 +6438,37 @@
         <v>2.574</v>
       </c>
       <c r="M63">
-        <v>42.59639600500397</v>
+        <v>43.2946975788565</v>
       </c>
       <c r="N63">
-        <v>-40.02239600500398</v>
+        <v>-40.7206975788565</v>
       </c>
       <c r="O63">
-        <v>-10.32577816929103</v>
+        <v>-10.50593997534498</v>
       </c>
       <c r="P63">
-        <v>-29.69661783571295</v>
+        <v>-30.21475760351152</v>
       </c>
       <c r="Q63">
-        <v>-29.28461783571295</v>
+        <v>-29.80275760351152</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1037547323778861</v>
+        <v>0.1052798569141463</v>
       </c>
       <c r="T63">
-        <v>1.338446475239864</v>
+        <v>1.373668750904071</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01559033303948969</v>
+        <v>0.01533887605498179</v>
       </c>
       <c r="W63">
-        <v>0.2321237994692883</v>
+        <v>0.2321830930262353</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.06042764743988249</v>
+        <v>0.0594530079650456</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6484,22 +6484,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1839598633036415</v>
+        <v>0.1858598633036415</v>
       </c>
       <c r="C64">
-        <v>-144.8791951963222</v>
+        <v>-148.2352137886517</v>
       </c>
       <c r="D64">
-        <v>29.088512941322</v>
+        <v>28.69390899637389</v>
       </c>
       <c r="E64">
-        <v>-112.2707566004916</v>
+        <v>-109.3093419531102</v>
       </c>
       <c r="F64">
-        <v>183.6077081376442</v>
+        <v>186.5691227850255</v>
       </c>
       <c r="G64">
         <v>9.640000000000001</v>
@@ -6520,37 +6520,37 @@
         <v>2.574</v>
       </c>
       <c r="M64">
-        <v>43.2946975788565</v>
+        <v>43.99299915270903</v>
       </c>
       <c r="N64">
-        <v>-40.7206975788565</v>
+        <v>-41.41899915270903</v>
       </c>
       <c r="O64">
-        <v>-10.50593997534498</v>
+        <v>-10.68610178139893</v>
       </c>
       <c r="P64">
-        <v>-30.21475760351152</v>
+        <v>-30.7328973713101</v>
       </c>
       <c r="Q64">
-        <v>-29.80275760351152</v>
+        <v>-30.3208973713101</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1052798569141463</v>
+        <v>0.1068874206145286</v>
       </c>
       <c r="T64">
-        <v>1.373668750904071</v>
+        <v>1.410794933360937</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01533887605498179</v>
+        <v>0.01509540183188684</v>
       </c>
       <c r="W64">
-        <v>0.2321830930262353</v>
+        <v>0.2322405042480411</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.0594530079650456</v>
+        <v>0.05850930942591792</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6566,22 +6566,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1858598633036415</v>
+        <v>0.1877598633036415</v>
       </c>
       <c r="C65">
-        <v>-148.2352137886517</v>
+        <v>-151.5806695714946</v>
       </c>
       <c r="D65">
-        <v>28.69390899637389</v>
+        <v>28.30986786091225</v>
       </c>
       <c r="E65">
-        <v>-109.3093419531102</v>
+        <v>-106.3479273057289</v>
       </c>
       <c r="F65">
-        <v>186.5691227850255</v>
+        <v>189.5305374324069</v>
       </c>
       <c r="G65">
         <v>9.640000000000001</v>
@@ -6602,37 +6602,37 @@
         <v>2.574</v>
       </c>
       <c r="M65">
-        <v>43.99299915270903</v>
+        <v>44.69130072656155</v>
       </c>
       <c r="N65">
-        <v>-41.41899915270903</v>
+        <v>-42.11730072656155</v>
       </c>
       <c r="O65">
-        <v>-10.68610178139893</v>
+        <v>-10.86626358745288</v>
       </c>
       <c r="P65">
-        <v>-30.7328973713101</v>
+        <v>-31.25103713910867</v>
       </c>
       <c r="Q65">
-        <v>-30.3208973713101</v>
+        <v>-30.83903713910867</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1068874206145286</v>
+        <v>0.1085842934093766</v>
       </c>
       <c r="T65">
-        <v>1.410794933360937</v>
+        <v>1.449983681509853</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01509540183188684</v>
+        <v>0.01485953617826361</v>
       </c>
       <c r="W65">
-        <v>0.2322405042480411</v>
+        <v>0.2322961213691654</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.05850930942591792</v>
+        <v>0.057595101466138</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6648,22 +6648,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1877598633036415</v>
+        <v>0.1896598633036415</v>
       </c>
       <c r="C66">
-        <v>-151.5806695714946</v>
+        <v>-154.9159810633503</v>
       </c>
       <c r="D66">
-        <v>28.30986786091225</v>
+        <v>27.93597101643794</v>
       </c>
       <c r="E66">
-        <v>-106.3479273057289</v>
+        <v>-103.3865126583475</v>
       </c>
       <c r="F66">
-        <v>189.5305374324069</v>
+        <v>192.4919520797883</v>
       </c>
       <c r="G66">
         <v>9.640000000000001</v>
@@ -6684,37 +6684,37 @@
         <v>2.574</v>
       </c>
       <c r="M66">
-        <v>44.69130072656155</v>
+        <v>45.38960230041408</v>
       </c>
       <c r="N66">
-        <v>-42.11730072656155</v>
+        <v>-42.81560230041408</v>
       </c>
       <c r="O66">
-        <v>-10.86626358745288</v>
+        <v>-11.04642539350683</v>
       </c>
       <c r="P66">
-        <v>-31.25103713910867</v>
+        <v>-31.76917690690725</v>
       </c>
       <c r="Q66">
-        <v>-30.83903713910867</v>
+        <v>-31.35717690690725</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1085842934093766</v>
+        <v>0.1103781303639302</v>
       </c>
       <c r="T66">
-        <v>1.449983681509853</v>
+        <v>1.491411786695849</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01485953617826361</v>
+        <v>0.01463092792936724</v>
       </c>
       <c r="W66">
-        <v>0.2322961213691654</v>
+        <v>0.2323500271942552</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.057595101466138</v>
+        <v>0.0567090229820435</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6730,22 +6730,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1896598633036415</v>
+        <v>0.1915598633036414</v>
       </c>
       <c r="C67">
-        <v>-154.9159810633503</v>
+        <v>-158.2415449609313</v>
       </c>
       <c r="D67">
-        <v>27.93597101643794</v>
+        <v>27.57182176623827</v>
       </c>
       <c r="E67">
-        <v>-103.3865126583475</v>
+        <v>-100.4250980109662</v>
       </c>
       <c r="F67">
-        <v>192.4919520797883</v>
+        <v>195.4533667271696</v>
       </c>
       <c r="G67">
         <v>9.640000000000001</v>
@@ -6766,37 +6766,37 @@
         <v>2.574</v>
       </c>
       <c r="M67">
-        <v>45.38960230041408</v>
+        <v>46.0879038742666</v>
       </c>
       <c r="N67">
-        <v>-42.81560230041408</v>
+        <v>-43.5139038742666</v>
       </c>
       <c r="O67">
-        <v>-11.04642539350683</v>
+        <v>-11.22658719956078</v>
       </c>
       <c r="P67">
-        <v>-31.76917690690725</v>
+        <v>-32.28731667470582</v>
       </c>
       <c r="Q67">
-        <v>-31.35717690690725</v>
+        <v>-31.87531667470582</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1103781303639302</v>
+        <v>0.1122774871393399</v>
       </c>
       <c r="T67">
-        <v>1.491411786695849</v>
+        <v>1.535276839245726</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01463092792936724</v>
+        <v>0.01440924720316471</v>
       </c>
       <c r="W67">
-        <v>0.2323500271942552</v>
+        <v>0.2324022995094938</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.0567090229820435</v>
+        <v>0.05584979536110346</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6812,22 +6812,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1915598633036414</v>
+        <v>0.1934598633036415</v>
       </c>
       <c r="C68">
-        <v>-158.2415449609313</v>
+        <v>-161.5577375431137</v>
       </c>
       <c r="D68">
-        <v>27.57182176623827</v>
+        <v>27.21704383143734</v>
       </c>
       <c r="E68">
-        <v>-100.4250980109662</v>
+        <v>-97.46368336358481</v>
       </c>
       <c r="F68">
-        <v>195.4533667271696</v>
+        <v>198.414781374551</v>
       </c>
       <c r="G68">
         <v>9.640000000000001</v>
@@ -6848,37 +6848,37 @@
         <v>2.574</v>
       </c>
       <c r="M68">
-        <v>46.0879038742666</v>
+        <v>46.78620544811913</v>
       </c>
       <c r="N68">
-        <v>-43.5139038742666</v>
+        <v>-44.21220544811913</v>
       </c>
       <c r="O68">
-        <v>-11.22658719956078</v>
+        <v>-11.40674900561473</v>
       </c>
       <c r="P68">
-        <v>-32.28731667470582</v>
+        <v>-32.80545644250439</v>
       </c>
       <c r="Q68">
-        <v>-31.87531667470582</v>
+        <v>-32.39345644250439</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1122774871393399</v>
+        <v>0.1142919564465927</v>
       </c>
       <c r="T68">
-        <v>1.535276839245726</v>
+        <v>1.58180037982893</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01440924720316471</v>
+        <v>0.0141941838120727</v>
       </c>
       <c r="W68">
-        <v>0.2324022995094938</v>
+        <v>0.2324530114571133</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.05584979536110346</v>
+        <v>0.05501621632586318</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6894,22 +6894,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1934598633036415</v>
+        <v>0.1953598633036415</v>
       </c>
       <c r="C69">
-        <v>-161.5577375431137</v>
+        <v>-164.8649159678712</v>
       </c>
       <c r="D69">
-        <v>27.21704383143734</v>
+        <v>26.87128005406115</v>
       </c>
       <c r="E69">
-        <v>-97.46368336358481</v>
+        <v>-94.50226871620345</v>
       </c>
       <c r="F69">
-        <v>198.414781374551</v>
+        <v>201.3761960219323</v>
       </c>
       <c r="G69">
         <v>9.640000000000001</v>
@@ -6930,37 +6930,37 @@
         <v>2.574</v>
       </c>
       <c r="M69">
-        <v>46.78620544811913</v>
+        <v>47.48450702197165</v>
       </c>
       <c r="N69">
-        <v>-44.21220544811913</v>
+        <v>-44.91050702197165</v>
       </c>
       <c r="O69">
-        <v>-11.40674900561473</v>
+        <v>-11.58691081166869</v>
       </c>
       <c r="P69">
-        <v>-32.80545644250439</v>
+        <v>-33.32359621030297</v>
       </c>
       <c r="Q69">
-        <v>-32.39345644250439</v>
+        <v>-32.91159621030297</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1142919564465927</v>
+        <v>0.1164323300855487</v>
       </c>
       <c r="T69">
-        <v>1.58180037982893</v>
+        <v>1.631231641698584</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0141941838120727</v>
+        <v>0.01398544581483633</v>
       </c>
       <c r="W69">
-        <v>0.2324530114571133</v>
+        <v>0.2325022318768616</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.05501621632586318</v>
+        <v>0.05420715432107104</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6976,22 +6976,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1953598633036415</v>
+        <v>0.1972598633036415</v>
       </c>
       <c r="C70">
-        <v>-164.8649159678712</v>
+        <v>-168.1634194715944</v>
       </c>
       <c r="D70">
-        <v>26.87128005406115</v>
+        <v>26.53419119771932</v>
       </c>
       <c r="E70">
-        <v>-94.50226871620345</v>
+        <v>-91.54085406882209</v>
       </c>
       <c r="F70">
-        <v>201.3761960219323</v>
+        <v>204.3376106693137</v>
       </c>
       <c r="G70">
         <v>9.640000000000001</v>
@@ -7012,37 +7012,37 @@
         <v>2.574</v>
       </c>
       <c r="M70">
-        <v>47.48450702197165</v>
+        <v>48.18280859582417</v>
       </c>
       <c r="N70">
-        <v>-44.91050702197165</v>
+        <v>-45.60880859582417</v>
       </c>
       <c r="O70">
-        <v>-11.58691081166869</v>
+        <v>-11.76707261772264</v>
       </c>
       <c r="P70">
-        <v>-33.32359621030297</v>
+        <v>-33.84173597810154</v>
       </c>
       <c r="Q70">
-        <v>-32.91159621030297</v>
+        <v>-33.42973597810154</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1164323300855487</v>
+        <v>0.1187107923463729</v>
       </c>
       <c r="T70">
-        <v>1.631231641698584</v>
+        <v>1.683852017237248</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01398544581483633</v>
+        <v>0.01378275819433146</v>
       </c>
       <c r="W70">
-        <v>0.2325022318768616</v>
+        <v>0.2325500256177766</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.05420715432107104</v>
+        <v>0.05342154338888161</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7058,22 +7058,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1972598633036415</v>
+        <v>0.1991598633036415</v>
       </c>
       <c r="C71">
-        <v>-168.1634194715944</v>
+        <v>-171.453570479257</v>
       </c>
       <c r="D71">
-        <v>26.53419119771932</v>
+        <v>26.20545483743808</v>
       </c>
       <c r="E71">
-        <v>-91.54085406882209</v>
+        <v>-88.57943942144072</v>
       </c>
       <c r="F71">
-        <v>204.3376106693137</v>
+        <v>207.2990253166951</v>
       </c>
       <c r="G71">
         <v>9.640000000000001</v>
@@ -7094,37 +7094,37 @@
         <v>2.574</v>
       </c>
       <c r="M71">
-        <v>48.18280859582417</v>
+        <v>48.8811101696767</v>
       </c>
       <c r="N71">
-        <v>-45.60880859582417</v>
+        <v>-46.3071101696767</v>
       </c>
       <c r="O71">
-        <v>-11.76707261772264</v>
+        <v>-11.94723442377659</v>
       </c>
       <c r="P71">
-        <v>-33.84173597810154</v>
+        <v>-34.35987574590011</v>
       </c>
       <c r="Q71">
-        <v>-33.42973597810154</v>
+        <v>-33.94787574590011</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1187107923463729</v>
+        <v>0.121141152091252</v>
       </c>
       <c r="T71">
-        <v>1.683852017237248</v>
+        <v>1.739980417811823</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01378275819433146</v>
+        <v>0.01358586164869816</v>
       </c>
       <c r="W71">
-        <v>0.2325500256177766</v>
+        <v>0.232596453823237</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.05342154338888161</v>
+        <v>0.05265837848332611</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7140,22 +7140,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1991598633036415</v>
+        <v>0.2010598633036415</v>
       </c>
       <c r="C72">
-        <v>-171.453570479257</v>
+        <v>-174.7356756330686</v>
       </c>
       <c r="D72">
-        <v>26.20545483743808</v>
+        <v>25.88476433100785</v>
       </c>
       <c r="E72">
-        <v>-88.57943942144072</v>
+        <v>-85.61802477405936</v>
       </c>
       <c r="F72">
-        <v>207.2990253166951</v>
+        <v>210.2604399640764</v>
       </c>
       <c r="G72">
         <v>9.640000000000001</v>
@@ -7176,37 +7176,37 @@
         <v>2.574</v>
       </c>
       <c r="M72">
-        <v>48.8811101696767</v>
+        <v>49.57941174352922</v>
       </c>
       <c r="N72">
-        <v>-46.3071101696767</v>
+        <v>-47.00541174352922</v>
       </c>
       <c r="O72">
-        <v>-11.94723442377659</v>
+        <v>-12.12739622983054</v>
       </c>
       <c r="P72">
-        <v>-34.35987574590011</v>
+        <v>-34.87801551369868</v>
       </c>
       <c r="Q72">
-        <v>-33.94787574590011</v>
+        <v>-34.46601551369869</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.121141152091252</v>
+        <v>0.1237391228530192</v>
       </c>
       <c r="T72">
-        <v>1.739980417811823</v>
+        <v>1.799979742563955</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01358586164869816</v>
+        <v>0.01339451148463198</v>
       </c>
       <c r="W72">
-        <v>0.232596453823237</v>
+        <v>0.2326415741919238</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.05265837848332611</v>
+        <v>0.05191671118074404</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7222,22 +7222,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2010598633036415</v>
+        <v>0.2029598633036415</v>
       </c>
       <c r="C73">
-        <v>-174.7356756330685</v>
+        <v>-178.0100267465112</v>
       </c>
       <c r="D73">
-        <v>25.88476433100785</v>
+        <v>25.57182786494657</v>
       </c>
       <c r="E73">
-        <v>-85.61802477405939</v>
+        <v>-82.65661012667803</v>
       </c>
       <c r="F73">
-        <v>210.2604399640764</v>
+        <v>213.2218546114578</v>
       </c>
       <c r="G73">
         <v>9.640000000000001</v>
@@ -7258,37 +7258,37 @@
         <v>2.574</v>
       </c>
       <c r="M73">
-        <v>49.57941174352921</v>
+        <v>50.27771331738174</v>
       </c>
       <c r="N73">
-        <v>-47.00541174352922</v>
+        <v>-47.70371331738174</v>
       </c>
       <c r="O73">
-        <v>-12.12739622983054</v>
+        <v>-12.30755803588449</v>
       </c>
       <c r="P73">
-        <v>-34.87801551369868</v>
+        <v>-35.39615528149725</v>
       </c>
       <c r="Q73">
-        <v>-34.46601551369868</v>
+        <v>-34.98415528149725</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1237391228530192</v>
+        <v>0.1265226629549128</v>
       </c>
       <c r="T73">
-        <v>1.799979742563955</v>
+        <v>1.86426473336981</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01339451148463199</v>
+        <v>0.01320847660290098</v>
       </c>
       <c r="W73">
-        <v>0.2326415741919238</v>
+        <v>0.2326854412170359</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.05191671118074415</v>
+        <v>0.05119564574767821</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7304,22 +7304,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2029598633036415</v>
+        <v>0.2048598633036415</v>
       </c>
       <c r="C74">
-        <v>-178.0100267465112</v>
+        <v>-181.2769016899991</v>
       </c>
       <c r="D74">
-        <v>25.57182786494657</v>
+        <v>25.26636756884004</v>
       </c>
       <c r="E74">
-        <v>-82.65661012667803</v>
+        <v>-79.69519547929667</v>
       </c>
       <c r="F74">
-        <v>213.2218546114578</v>
+        <v>216.1832692588391</v>
       </c>
       <c r="G74">
         <v>9.640000000000001</v>
@@ -7340,37 +7340,37 @@
         <v>2.574</v>
       </c>
       <c r="M74">
-        <v>50.27771331738174</v>
+        <v>50.97601489123426</v>
       </c>
       <c r="N74">
-        <v>-47.70371331738174</v>
+        <v>-48.40201489123427</v>
       </c>
       <c r="O74">
-        <v>-12.30755803588449</v>
+        <v>-12.48771984193844</v>
       </c>
       <c r="P74">
-        <v>-35.39615528149725</v>
+        <v>-35.91429504929582</v>
       </c>
       <c r="Q74">
-        <v>-34.98415528149725</v>
+        <v>-35.50229504929582</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1265226629549128</v>
+        <v>0.1295123912125021</v>
       </c>
       <c r="T74">
-        <v>1.86426473336981</v>
+        <v>1.93331157534647</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01320847660290098</v>
+        <v>0.01302753856724481</v>
       </c>
       <c r="W74">
-        <v>0.2326854412170359</v>
+        <v>0.2327281064058437</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.05119564574767821</v>
+        <v>0.05049433553195659</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7386,22 +7386,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2048598633036415</v>
+        <v>0.2067598633036414</v>
       </c>
       <c r="C75">
-        <v>-181.2769016899991</v>
+        <v>-184.5365652138115</v>
       </c>
       <c r="D75">
-        <v>25.26636756884004</v>
+        <v>24.96811869240903</v>
       </c>
       <c r="E75">
-        <v>-79.69519547929667</v>
+        <v>-76.73378083191531</v>
       </c>
       <c r="F75">
-        <v>216.1832692588391</v>
+        <v>219.1446839062205</v>
       </c>
       <c r="G75">
         <v>9.640000000000001</v>
@@ -7422,37 +7422,37 @@
         <v>2.574</v>
       </c>
       <c r="M75">
-        <v>50.97601489123426</v>
+        <v>51.67431646508679</v>
       </c>
       <c r="N75">
-        <v>-48.40201489123427</v>
+        <v>-49.10031646508679</v>
       </c>
       <c r="O75">
-        <v>-12.48771984193844</v>
+        <v>-12.66788164799239</v>
       </c>
       <c r="P75">
-        <v>-35.91429504929582</v>
+        <v>-36.4324348170944</v>
       </c>
       <c r="Q75">
-        <v>-35.50229504929582</v>
+        <v>-36.0204348170944</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1295123912125021</v>
+        <v>0.1327320985668291</v>
       </c>
       <c r="T75">
-        <v>1.93331157534647</v>
+        <v>2.007669712859795</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01302753856724481</v>
+        <v>0.01285149074876853</v>
       </c>
       <c r="W75">
-        <v>0.2327281064058437</v>
+        <v>0.2327696184814404</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.05049433553195659</v>
+        <v>0.04981197964638961</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7468,22 +7468,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2067598633036414</v>
+        <v>0.2086598633036414</v>
       </c>
       <c r="C76">
-        <v>-184.5365652138115</v>
+        <v>-187.7892697134207</v>
       </c>
       <c r="D76">
-        <v>24.96811869240903</v>
+        <v>24.67682884018112</v>
       </c>
       <c r="E76">
-        <v>-76.73378083191531</v>
+        <v>-73.77236618453395</v>
       </c>
       <c r="F76">
-        <v>219.1446839062205</v>
+        <v>222.1060985536018</v>
       </c>
       <c r="G76">
         <v>9.640000000000001</v>
@@ -7504,37 +7504,37 @@
         <v>2.574</v>
       </c>
       <c r="M76">
-        <v>51.67431646508679</v>
+        <v>52.37261803893931</v>
       </c>
       <c r="N76">
-        <v>-49.10031646508679</v>
+        <v>-49.79861803893932</v>
       </c>
       <c r="O76">
-        <v>-12.66788164799239</v>
+        <v>-12.84804345404634</v>
       </c>
       <c r="P76">
-        <v>-36.4324348170944</v>
+        <v>-36.95057458489298</v>
       </c>
       <c r="Q76">
-        <v>-36.0204348170944</v>
+        <v>-36.53857458489298</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1327320985668291</v>
+        <v>0.1362093825095023</v>
       </c>
       <c r="T76">
-        <v>2.007669712859795</v>
+        <v>2.087976501374187</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01285149074876853</v>
+        <v>0.01268013753878494</v>
       </c>
       <c r="W76">
-        <v>0.2327696184814404</v>
+        <v>0.2328100235683545</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.04981197964638961</v>
+        <v>0.04914781991777106</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7550,22 +7550,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2086598633036414</v>
+        <v>0.2105598633036415</v>
       </c>
       <c r="C77">
-        <v>-187.7892697134207</v>
+        <v>-191.0352559418669</v>
       </c>
       <c r="D77">
-        <v>24.67682884018112</v>
+        <v>24.3922572591163</v>
       </c>
       <c r="E77">
-        <v>-73.77236618453395</v>
+        <v>-70.81095153715262</v>
       </c>
       <c r="F77">
-        <v>222.1060985536018</v>
+        <v>225.0675132009832</v>
       </c>
       <c r="G77">
         <v>9.640000000000001</v>
@@ -7586,37 +7586,37 @@
         <v>2.574</v>
       </c>
       <c r="M77">
-        <v>52.37261803893931</v>
+        <v>53.07091961279183</v>
       </c>
       <c r="N77">
-        <v>-49.79861803893932</v>
+        <v>-50.49691961279184</v>
       </c>
       <c r="O77">
-        <v>-12.84804345404634</v>
+        <v>-13.02820526010029</v>
       </c>
       <c r="P77">
-        <v>-36.95057458489298</v>
+        <v>-37.46871435269154</v>
       </c>
       <c r="Q77">
-        <v>-36.53857458489298</v>
+        <v>-37.05671435269154</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1362093825095023</v>
+        <v>0.1399764401140649</v>
       </c>
       <c r="T77">
-        <v>2.087976501374187</v>
+        <v>2.174975522264779</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01268013753878494</v>
+        <v>0.01251329362380093</v>
       </c>
       <c r="W77">
-        <v>0.2328100235683545</v>
+        <v>0.2328493653635078</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.04914781991777106</v>
+        <v>0.04850113807674772</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7632,22 +7632,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2105598633036415</v>
+        <v>0.2124598633036415</v>
       </c>
       <c r="C78">
-        <v>-191.0352559418669</v>
+        <v>-194.2747536734032</v>
       </c>
       <c r="D78">
-        <v>24.3922572591163</v>
+        <v>24.11417417496132</v>
       </c>
       <c r="E78">
-        <v>-70.81095153715262</v>
+        <v>-67.84953688977126</v>
       </c>
       <c r="F78">
-        <v>225.0675132009832</v>
+        <v>228.0289278483645</v>
       </c>
       <c r="G78">
         <v>9.640000000000001</v>
@@ -7668,37 +7668,37 @@
         <v>2.574</v>
       </c>
       <c r="M78">
-        <v>53.07091961279183</v>
+        <v>53.76922118664436</v>
       </c>
       <c r="N78">
-        <v>-50.49691961279184</v>
+        <v>-51.19522118664436</v>
       </c>
       <c r="O78">
-        <v>-13.02820526010029</v>
+        <v>-13.20836706615425</v>
       </c>
       <c r="P78">
-        <v>-37.46871435269154</v>
+        <v>-37.98685412049011</v>
       </c>
       <c r="Q78">
-        <v>-37.05671435269154</v>
+        <v>-37.57485412049012</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1399764401140649</v>
+        <v>0.1440710679451112</v>
       </c>
       <c r="T78">
-        <v>2.174975522264779</v>
+        <v>2.269539675406726</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01251329362380093</v>
+        <v>0.01235078331699832</v>
       </c>
       <c r="W78">
-        <v>0.2328493653635078</v>
+        <v>0.2328876852938518</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.04850113807674772</v>
+        <v>0.04787125316666019</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7714,22 +7714,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2124598633036415</v>
+        <v>0.2143598633036415</v>
       </c>
       <c r="C79">
-        <v>-194.2747536734032</v>
+        <v>-197.5079823222583</v>
       </c>
       <c r="D79">
-        <v>24.11417417496132</v>
+        <v>23.84236017348761</v>
       </c>
       <c r="E79">
-        <v>-67.84953688977126</v>
+        <v>-64.8881222423899</v>
       </c>
       <c r="F79">
-        <v>228.0289278483645</v>
+        <v>230.9903424957459</v>
       </c>
       <c r="G79">
         <v>9.640000000000001</v>
@@ -7750,37 +7750,37 @@
         <v>2.574</v>
       </c>
       <c r="M79">
-        <v>53.76922118664436</v>
+        <v>54.46752276049688</v>
       </c>
       <c r="N79">
-        <v>-51.19522118664436</v>
+        <v>-51.89352276049689</v>
       </c>
       <c r="O79">
-        <v>-13.20836706615425</v>
+        <v>-13.3885288722082</v>
       </c>
       <c r="P79">
-        <v>-37.98685412049011</v>
+        <v>-38.50499388828869</v>
       </c>
       <c r="Q79">
-        <v>-37.57485412049012</v>
+        <v>-38.09299388828869</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1440710679451112</v>
+        <v>0.148537934669889</v>
       </c>
       <c r="T79">
-        <v>2.269539675406726</v>
+        <v>2.372700569743395</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01235078331699832</v>
+        <v>0.01219243994113937</v>
       </c>
       <c r="W79">
-        <v>0.2328876852938518</v>
+        <v>0.2329250226618793</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.04787125316666019</v>
+        <v>0.04725751915170295</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7796,22 +7796,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2143598633036415</v>
+        <v>0.2162598633036415</v>
       </c>
       <c r="C80">
-        <v>-197.5079823222583</v>
+        <v>-200.7351515200169</v>
       </c>
       <c r="D80">
-        <v>23.84236017348761</v>
+        <v>23.57660562311035</v>
       </c>
       <c r="E80">
-        <v>-64.8881222423899</v>
+        <v>-61.92670759500854</v>
       </c>
       <c r="F80">
-        <v>230.9903424957459</v>
+        <v>233.9517571431273</v>
       </c>
       <c r="G80">
         <v>9.640000000000001</v>
@@ -7832,37 +7832,37 @@
         <v>2.574</v>
       </c>
       <c r="M80">
-        <v>54.46752276049688</v>
+        <v>55.16582433434941</v>
       </c>
       <c r="N80">
-        <v>-51.89352276049689</v>
+        <v>-52.59182433434941</v>
       </c>
       <c r="O80">
-        <v>-13.3885288722082</v>
+        <v>-13.56869067826215</v>
       </c>
       <c r="P80">
-        <v>-38.50499388828869</v>
+        <v>-39.02313365608726</v>
       </c>
       <c r="Q80">
-        <v>-38.09299388828869</v>
+        <v>-38.61113365608726</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.148537934669889</v>
+        <v>0.1534302172732171</v>
       </c>
       <c r="T80">
-        <v>2.372700569743395</v>
+        <v>2.485686311159748</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01219243994113937</v>
+        <v>0.01203810525834014</v>
       </c>
       <c r="W80">
-        <v>0.2329250226618793</v>
+        <v>0.2329614147800834</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.04725751915170295</v>
+        <v>0.04665932270674467</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7878,22 +7878,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2162598633036415</v>
+        <v>0.2181598633036415</v>
       </c>
       <c r="C81">
-        <v>-200.7351515200169</v>
+        <v>-203.9564616548122</v>
       </c>
       <c r="D81">
-        <v>23.57660562311035</v>
+        <v>23.31671013569636</v>
       </c>
       <c r="E81">
-        <v>-61.92670759500854</v>
+        <v>-58.96529294762718</v>
       </c>
       <c r="F81">
-        <v>233.9517571431273</v>
+        <v>236.9131717905086</v>
       </c>
       <c r="G81">
         <v>9.640000000000001</v>
@@ -7914,37 +7914,37 @@
         <v>2.574</v>
       </c>
       <c r="M81">
-        <v>55.16582433434941</v>
+        <v>55.86412590820193</v>
       </c>
       <c r="N81">
-        <v>-52.59182433434941</v>
+        <v>-53.29012590820194</v>
       </c>
       <c r="O81">
-        <v>-13.56869067826215</v>
+        <v>-13.7488524843161</v>
       </c>
       <c r="P81">
-        <v>-39.02313365608726</v>
+        <v>-39.54127342388584</v>
       </c>
       <c r="Q81">
-        <v>-38.61113365608726</v>
+        <v>-39.12927342388584</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1534302172732171</v>
+        <v>0.1588117281368779</v>
       </c>
       <c r="T81">
-        <v>2.485686311159748</v>
+        <v>2.609970626717735</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01203810525834014</v>
+        <v>0.01188762894261089</v>
       </c>
       <c r="W81">
-        <v>0.2329614147800834</v>
+        <v>0.2329968970953324</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.04665932270674467</v>
+        <v>0.0460760811729104</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7960,22 +7960,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2181598633036415</v>
+        <v>0.2200598633036415</v>
       </c>
       <c r="C82">
-        <v>-203.9564616548122</v>
+        <v>-207.1721043752447</v>
       </c>
       <c r="D82">
-        <v>23.31671013569636</v>
+        <v>23.0624820626453</v>
       </c>
       <c r="E82">
-        <v>-58.96529294762718</v>
+        <v>-56.00387830024582</v>
       </c>
       <c r="F82">
-        <v>236.9131717905086</v>
+        <v>239.87458643789</v>
       </c>
       <c r="G82">
         <v>9.640000000000001</v>
@@ -7996,37 +7996,37 @@
         <v>2.574</v>
       </c>
       <c r="M82">
-        <v>55.86412590820193</v>
+        <v>56.56242748205446</v>
       </c>
       <c r="N82">
-        <v>-53.29012590820194</v>
+        <v>-53.98842748205446</v>
       </c>
       <c r="O82">
-        <v>-13.7488524843161</v>
+        <v>-13.92901429037005</v>
       </c>
       <c r="P82">
-        <v>-39.54127342388584</v>
+        <v>-40.05941319168441</v>
       </c>
       <c r="Q82">
-        <v>-39.12927342388584</v>
+        <v>-39.64741319168441</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1588117281368779</v>
+        <v>0.1647597138282925</v>
       </c>
       <c r="T82">
-        <v>2.609970626717735</v>
+        <v>2.747337501808142</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01188762894261089</v>
+        <v>0.01174086809146754</v>
       </c>
       <c r="W82">
-        <v>0.2329968970953324</v>
+        <v>0.233031503304032</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.0460760811729104</v>
+        <v>0.04550724066460288</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8042,22 +8042,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2200598633036415</v>
+        <v>0.2219598633036415</v>
       </c>
       <c r="C83">
-        <v>-207.1721043752447</v>
+        <v>-210.3822630616896</v>
       </c>
       <c r="D83">
-        <v>23.0624820626453</v>
+        <v>22.81373802358178</v>
       </c>
       <c r="E83">
-        <v>-56.00387830024582</v>
+        <v>-53.04246365286446</v>
       </c>
       <c r="F83">
-        <v>239.87458643789</v>
+        <v>242.8360010852713</v>
       </c>
       <c r="G83">
         <v>9.640000000000001</v>
@@ -8078,37 +8078,37 @@
         <v>2.574</v>
       </c>
       <c r="M83">
-        <v>56.56242748205446</v>
+        <v>57.26072905590699</v>
       </c>
       <c r="N83">
-        <v>-53.98842748205446</v>
+        <v>-54.68672905590699</v>
       </c>
       <c r="O83">
-        <v>-13.92901429037005</v>
+        <v>-14.109176096424</v>
       </c>
       <c r="P83">
-        <v>-40.05941319168441</v>
+        <v>-40.57755295948299</v>
       </c>
       <c r="Q83">
-        <v>-39.64741319168441</v>
+        <v>-40.16555295948299</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1647597138282925</v>
+        <v>0.1713685868187532</v>
       </c>
       <c r="T83">
-        <v>2.747337501808142</v>
+        <v>2.899967363019706</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01174086809146754</v>
+        <v>0.01159768677327891</v>
       </c>
       <c r="W83">
-        <v>0.233031503304032</v>
+        <v>0.2330652654588609</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.04550724066460288</v>
+        <v>0.04495227431503457</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8124,22 +8124,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2219598633036415</v>
+        <v>0.2238598633036415</v>
       </c>
       <c r="C84">
-        <v>-210.3822630616896</v>
+        <v>-213.5871132674308</v>
       </c>
       <c r="D84">
-        <v>22.81373802358178</v>
+        <v>22.57030246522191</v>
       </c>
       <c r="E84">
-        <v>-53.04246365286446</v>
+        <v>-50.0810490054831</v>
       </c>
       <c r="F84">
-        <v>242.8360010852713</v>
+        <v>245.7974157326527</v>
       </c>
       <c r="G84">
         <v>9.640000000000001</v>
@@ -8160,37 +8160,37 @@
         <v>2.574</v>
       </c>
       <c r="M84">
-        <v>57.26072905590699</v>
+        <v>57.95903062975951</v>
       </c>
       <c r="N84">
-        <v>-54.68672905590699</v>
+        <v>-55.38503062975951</v>
       </c>
       <c r="O84">
-        <v>-14.109176096424</v>
+        <v>-14.28933790247796</v>
       </c>
       <c r="P84">
-        <v>-40.57755295948299</v>
+        <v>-41.09569272728156</v>
       </c>
       <c r="Q84">
-        <v>-40.16555295948299</v>
+        <v>-40.68369272728156</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1713685868187532</v>
+        <v>0.1787549742786799</v>
       </c>
       <c r="T84">
-        <v>2.899967363019706</v>
+        <v>3.070553678491453</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01159768677327891</v>
+        <v>0.01145795560733579</v>
       </c>
       <c r="W84">
-        <v>0.2330652654588609</v>
+        <v>0.2330982140677902</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.04495227431503457</v>
+        <v>0.04441068064858833</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8206,22 +8206,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2238598633036415</v>
+        <v>0.2257598633036415</v>
       </c>
       <c r="C85">
-        <v>-213.5871132674308</v>
+        <v>-216.7868231318493</v>
       </c>
       <c r="D85">
-        <v>22.57030246522191</v>
+        <v>22.33200724818474</v>
       </c>
       <c r="E85">
-        <v>-50.0810490054831</v>
+        <v>-47.11963435810173</v>
       </c>
       <c r="F85">
-        <v>245.7974157326527</v>
+        <v>248.7588303800341</v>
       </c>
       <c r="G85">
         <v>9.640000000000001</v>
@@ -8242,37 +8242,37 @@
         <v>2.574</v>
       </c>
       <c r="M85">
-        <v>57.95903062975951</v>
+        <v>58.65733220361204</v>
       </c>
       <c r="N85">
-        <v>-55.38503062975951</v>
+        <v>-56.08333220361204</v>
       </c>
       <c r="O85">
-        <v>-14.28933790247796</v>
+        <v>-14.46949970853191</v>
       </c>
       <c r="P85">
-        <v>-41.09569272728156</v>
+        <v>-41.61383249508013</v>
       </c>
       <c r="Q85">
-        <v>-40.68369272728156</v>
+        <v>-41.20183249508013</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1787549742786799</v>
+        <v>0.1870646601710975</v>
       </c>
       <c r="T85">
-        <v>3.070553678491453</v>
+        <v>3.26246328339717</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01145795560733579</v>
+        <v>0.01132155137391513</v>
       </c>
       <c r="W85">
-        <v>0.2330982140677902</v>
+        <v>0.2331303781860308</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.04441068064858833</v>
+        <v>0.0438819820694385</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8288,22 +8288,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2257598633036415</v>
+        <v>0.2276598633036415</v>
       </c>
       <c r="C86">
-        <v>-216.7868231318493</v>
+        <v>-219.9815537677108</v>
       </c>
       <c r="D86">
-        <v>22.33200724818474</v>
+        <v>22.09869125970461</v>
       </c>
       <c r="E86">
-        <v>-47.11963435810176</v>
+        <v>-44.1582197107204</v>
       </c>
       <c r="F86">
-        <v>248.758830380034</v>
+        <v>251.7202450274154</v>
       </c>
       <c r="G86">
         <v>9.640000000000001</v>
@@ -8324,37 +8324,37 @@
         <v>2.574</v>
       </c>
       <c r="M86">
-        <v>58.65733220361203</v>
+        <v>59.35563377746455</v>
       </c>
       <c r="N86">
-        <v>-56.08333220361203</v>
+        <v>-56.78163377746456</v>
       </c>
       <c r="O86">
-        <v>-14.4694997085319</v>
+        <v>-14.64966151458586</v>
       </c>
       <c r="P86">
-        <v>-41.61383249508012</v>
+        <v>-42.1319722628787</v>
       </c>
       <c r="Q86">
-        <v>-41.20183249508013</v>
+        <v>-41.7199722628787</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1870646601710974</v>
+        <v>0.1964823041825038</v>
       </c>
       <c r="T86">
-        <v>3.262463283397167</v>
+        <v>3.479960835623646</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01132155137391513</v>
+        <v>0.01118835665186907</v>
       </c>
       <c r="W86">
-        <v>0.2331303781860308</v>
+        <v>0.2331617855014893</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.0438819820694385</v>
+        <v>0.04336572345685685</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8370,22 +8370,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2276598633036415</v>
+        <v>0.2295598633036415</v>
       </c>
       <c r="C87">
-        <v>-219.9815537677108</v>
+        <v>-223.1714596244269</v>
       </c>
       <c r="D87">
-        <v>22.09869125970461</v>
+        <v>21.87020005036985</v>
       </c>
       <c r="E87">
-        <v>-44.1582197107204</v>
+        <v>-41.19680506333904</v>
       </c>
       <c r="F87">
-        <v>251.7202450274154</v>
+        <v>254.6816596747967</v>
       </c>
       <c r="G87">
         <v>9.640000000000001</v>
@@ -8406,37 +8406,37 @@
         <v>2.574</v>
       </c>
       <c r="M87">
-        <v>59.35563377746455</v>
+        <v>60.05393535131707</v>
       </c>
       <c r="N87">
-        <v>-56.78163377746456</v>
+        <v>-57.47993535131707</v>
       </c>
       <c r="O87">
-        <v>-14.64966151458586</v>
+        <v>-14.82982332063981</v>
       </c>
       <c r="P87">
-        <v>-42.1319722628787</v>
+        <v>-42.65011203067727</v>
       </c>
       <c r="Q87">
-        <v>-41.7199722628787</v>
+        <v>-42.23811203067727</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1964823041825038</v>
+        <v>0.2072453259098256</v>
       </c>
       <c r="T87">
-        <v>3.479960835623646</v>
+        <v>3.72852946673962</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01118835665186907</v>
+        <v>0.0110582594814985</v>
       </c>
       <c r="W87">
-        <v>0.2331617855014893</v>
+        <v>0.2331924624142627</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.04336572345685685</v>
+        <v>0.04286147085852132</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8452,22 +8452,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2295598633036415</v>
+        <v>0.2314598633036415</v>
       </c>
       <c r="C88">
-        <v>-223.1714596244269</v>
+        <v>-226.3566888290114</v>
       </c>
       <c r="D88">
-        <v>21.87020005036985</v>
+        <v>21.64638549316668</v>
       </c>
       <c r="E88">
-        <v>-41.19680506333904</v>
+        <v>-38.23539041595768</v>
       </c>
       <c r="F88">
-        <v>254.6816596747967</v>
+        <v>257.6430743221781</v>
       </c>
       <c r="G88">
         <v>9.640000000000001</v>
@@ -8488,37 +8488,37 @@
         <v>2.574</v>
       </c>
       <c r="M88">
-        <v>60.05393535131707</v>
+        <v>60.7522369251696</v>
       </c>
       <c r="N88">
-        <v>-57.47993535131707</v>
+        <v>-58.1782369251696</v>
       </c>
       <c r="O88">
-        <v>-14.82982332063981</v>
+        <v>-15.00998512669376</v>
       </c>
       <c r="P88">
-        <v>-42.65011203067727</v>
+        <v>-43.16825179847584</v>
       </c>
       <c r="Q88">
-        <v>-42.23811203067727</v>
+        <v>-42.75625179847584</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2072453259098256</v>
+        <v>0.2196641971336583</v>
       </c>
       <c r="T88">
-        <v>3.72852946673962</v>
+        <v>4.01533942571959</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0110582594814985</v>
+        <v>0.01093115305067668</v>
       </c>
       <c r="W88">
-        <v>0.2331924624142627</v>
+        <v>0.2332224341106504</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.04286147085852132</v>
+        <v>0.04236881027394057</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8534,22 +8534,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2314598633036415</v>
+        <v>0.2333598633036415</v>
       </c>
       <c r="C89">
-        <v>-226.3566888290114</v>
+        <v>-229.5373835063128</v>
       </c>
       <c r="D89">
-        <v>21.64638549316668</v>
+        <v>21.42710546324667</v>
       </c>
       <c r="E89">
-        <v>-38.23539041595768</v>
+        <v>-35.27397576857629</v>
       </c>
       <c r="F89">
-        <v>257.6430743221781</v>
+        <v>260.6044889695595</v>
       </c>
       <c r="G89">
         <v>9.640000000000001</v>
@@ -8570,37 +8570,37 @@
         <v>2.574</v>
       </c>
       <c r="M89">
-        <v>60.7522369251696</v>
+        <v>61.45053849902213</v>
       </c>
       <c r="N89">
-        <v>-58.1782369251696</v>
+        <v>-58.87653849902213</v>
       </c>
       <c r="O89">
-        <v>-15.00998512669376</v>
+        <v>-15.19014693274771</v>
       </c>
       <c r="P89">
-        <v>-43.16825179847584</v>
+        <v>-43.68639156627442</v>
       </c>
       <c r="Q89">
-        <v>-42.75625179847584</v>
+        <v>-43.27439156627442</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2196641971336583</v>
+        <v>0.2341528802281299</v>
       </c>
       <c r="T89">
-        <v>4.01533942571959</v>
+        <v>4.349951044529558</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01093115305067668</v>
+        <v>0.01080693540237353</v>
       </c>
       <c r="W89">
-        <v>0.2332224341106504</v>
+        <v>0.2332517246321203</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.04236881027394057</v>
+        <v>0.0418873465208276</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8616,22 +8616,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2333598633036415</v>
+        <v>0.2352598633036415</v>
       </c>
       <c r="C90">
-        <v>-229.5373835063128</v>
+        <v>-232.713680079978</v>
       </c>
       <c r="D90">
-        <v>21.42710546324667</v>
+        <v>21.21222353696279</v>
       </c>
       <c r="E90">
-        <v>-35.27397576857629</v>
+        <v>-32.31256112119496</v>
       </c>
       <c r="F90">
-        <v>260.6044889695595</v>
+        <v>263.5659036169408</v>
       </c>
       <c r="G90">
         <v>9.640000000000001</v>
@@ -8652,37 +8652,37 @@
         <v>2.574</v>
       </c>
       <c r="M90">
-        <v>61.45053849902213</v>
+        <v>62.14884007287465</v>
       </c>
       <c r="N90">
-        <v>-58.87653849902213</v>
+        <v>-59.57484007287465</v>
       </c>
       <c r="O90">
-        <v>-15.19014693274771</v>
+        <v>-15.37030873880166</v>
       </c>
       <c r="P90">
-        <v>-43.68639156627442</v>
+        <v>-44.20453133407299</v>
       </c>
       <c r="Q90">
-        <v>-43.27439156627442</v>
+        <v>-43.79253133407299</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2341528802281299</v>
+        <v>0.251275869339778</v>
       </c>
       <c r="T90">
-        <v>4.349951044529558</v>
+        <v>4.745401139486789</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01080693540237353</v>
+        <v>0.01068550916189743</v>
       </c>
       <c r="W90">
-        <v>0.2332517246321203</v>
+        <v>0.2332803569396246</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.0418873465208276</v>
+        <v>0.04141670217789695</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8698,22 +8698,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2352598633036415</v>
+        <v>0.2371598633036414</v>
       </c>
       <c r="C91">
-        <v>-232.713680079978</v>
+        <v>-235.8857095554871</v>
       </c>
       <c r="D91">
-        <v>21.21222353696279</v>
+        <v>21.00160870883512</v>
       </c>
       <c r="E91">
-        <v>-32.31256112119496</v>
+        <v>-29.35114647381357</v>
       </c>
       <c r="F91">
-        <v>263.5659036169408</v>
+        <v>266.5273182643222</v>
       </c>
       <c r="G91">
         <v>9.640000000000001</v>
@@ -8734,37 +8734,37 @@
         <v>2.574</v>
       </c>
       <c r="M91">
-        <v>62.14884007287465</v>
+        <v>62.84714164672718</v>
       </c>
       <c r="N91">
-        <v>-59.57484007287465</v>
+        <v>-60.27314164672718</v>
       </c>
       <c r="O91">
-        <v>-15.37030873880166</v>
+        <v>-15.55047054485561</v>
       </c>
       <c r="P91">
-        <v>-44.20453133407299</v>
+        <v>-44.72267110187157</v>
       </c>
       <c r="Q91">
-        <v>-43.79253133407299</v>
+        <v>-44.31067110187157</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.251275869339778</v>
+        <v>0.2718234562737558</v>
       </c>
       <c r="T91">
-        <v>4.745401139486789</v>
+        <v>5.219941253435469</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01068550916189743</v>
+        <v>0.01056678128232079</v>
       </c>
       <c r="W91">
-        <v>0.2332803569396246</v>
+        <v>0.2333083529736288</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.04141670217789695</v>
+        <v>0.04095651659814259</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8780,22 +8780,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2371598633036414</v>
+        <v>0.2390598633036415</v>
       </c>
       <c r="C92">
-        <v>-235.8857095554871</v>
+        <v>-239.0535977864914</v>
       </c>
       <c r="D92">
-        <v>21.00160870883512</v>
+        <v>20.79513512521216</v>
       </c>
       <c r="E92">
-        <v>-29.35114647381357</v>
+        <v>-26.38973182643224</v>
       </c>
       <c r="F92">
-        <v>266.5273182643222</v>
+        <v>269.4887329117036</v>
       </c>
       <c r="G92">
         <v>9.640000000000001</v>
@@ -8816,37 +8816,37 @@
         <v>2.574</v>
       </c>
       <c r="M92">
-        <v>62.84714164672718</v>
+        <v>63.5454432205797</v>
       </c>
       <c r="N92">
-        <v>-60.27314164672718</v>
+        <v>-60.9714432205797</v>
       </c>
       <c r="O92">
-        <v>-15.55047054485561</v>
+        <v>-15.73063235090956</v>
       </c>
       <c r="P92">
-        <v>-44.72267110187157</v>
+        <v>-45.24081086967014</v>
       </c>
       <c r="Q92">
-        <v>-44.31067110187157</v>
+        <v>-44.82881086967014</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2718234562737558</v>
+        <v>0.2969371736375065</v>
       </c>
       <c r="T92">
-        <v>5.219941253435469</v>
+        <v>5.799934726039411</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01056678128232079</v>
+        <v>0.01045066280669089</v>
       </c>
       <c r="W92">
-        <v>0.2333083529736288</v>
+        <v>0.2333357337101823</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.04095651659814259</v>
+        <v>0.04050644498717393</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8862,22 +8862,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2390598633036415</v>
+        <v>0.2409598633036415</v>
       </c>
       <c r="C93">
-        <v>-239.0535977864914</v>
+        <v>-242.2174657255951</v>
       </c>
       <c r="D93">
-        <v>20.79513512521216</v>
+        <v>20.59268183348982</v>
       </c>
       <c r="E93">
-        <v>-26.38973182643224</v>
+        <v>-23.42831717905085</v>
       </c>
       <c r="F93">
-        <v>269.4887329117036</v>
+        <v>272.4501475590849</v>
       </c>
       <c r="G93">
         <v>9.640000000000001</v>
@@ -8898,37 +8898,37 @@
         <v>2.574</v>
       </c>
       <c r="M93">
-        <v>63.5454432205797</v>
+        <v>64.24374479443223</v>
       </c>
       <c r="N93">
-        <v>-60.9714432205797</v>
+        <v>-61.66974479443223</v>
       </c>
       <c r="O93">
-        <v>-15.73063235090956</v>
+        <v>-15.91079415696352</v>
       </c>
       <c r="P93">
-        <v>-45.24081086967014</v>
+        <v>-45.75895063746871</v>
       </c>
       <c r="Q93">
-        <v>-44.82881086967014</v>
+        <v>-45.34695063746872</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2969371736375065</v>
+        <v>0.3283293203421949</v>
       </c>
       <c r="T93">
-        <v>5.799934726039411</v>
+        <v>6.52492656679434</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01045066280669089</v>
+        <v>0.01033706864574859</v>
       </c>
       <c r="W93">
-        <v>0.2333357337101823</v>
+        <v>0.2333625192133325</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.04050644498717393</v>
+        <v>0.04006615754166121</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8944,22 +8944,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2409598633036415</v>
+        <v>0.2428598633036415</v>
       </c>
       <c r="C94">
-        <v>-242.2174657255951</v>
+        <v>-245.3774296606279</v>
       </c>
       <c r="D94">
-        <v>20.59268183348982</v>
+        <v>20.39413254583838</v>
       </c>
       <c r="E94">
-        <v>-23.42831717905085</v>
+        <v>-20.46690253166952</v>
       </c>
       <c r="F94">
-        <v>272.4501475590849</v>
+        <v>275.4115622064663</v>
       </c>
       <c r="G94">
         <v>9.640000000000001</v>
@@ -8980,37 +8980,37 @@
         <v>2.574</v>
       </c>
       <c r="M94">
-        <v>64.24374479443223</v>
+        <v>64.94204636828475</v>
       </c>
       <c r="N94">
-        <v>-61.66974479443223</v>
+        <v>-62.36804636828475</v>
       </c>
       <c r="O94">
-        <v>-15.91079415696352</v>
+        <v>-16.09095596301747</v>
       </c>
       <c r="P94">
-        <v>-45.75895063746871</v>
+        <v>-46.27709040526729</v>
       </c>
       <c r="Q94">
-        <v>-45.34695063746872</v>
+        <v>-45.86509040526729</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3283293203421949</v>
+        <v>0.3686906518196513</v>
       </c>
       <c r="T94">
-        <v>6.52492656679434</v>
+        <v>7.457058933479245</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01033706864574859</v>
+        <v>0.01022591736998786</v>
       </c>
       <c r="W94">
-        <v>0.2333625192133325</v>
+        <v>0.2333887286841569</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.04006615754166121</v>
+        <v>0.03963533864336377</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9026,22 +9026,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2428598633036415</v>
+        <v>0.2447598633036415</v>
       </c>
       <c r="C95">
-        <v>-245.3774296606279</v>
+        <v>-248.5336014373804</v>
       </c>
       <c r="D95">
-        <v>20.39413254583838</v>
+        <v>20.19937541646723</v>
       </c>
       <c r="E95">
-        <v>-20.46690253166952</v>
+        <v>-17.50548788428813</v>
       </c>
       <c r="F95">
-        <v>275.4115622064663</v>
+        <v>278.3729768538477</v>
       </c>
       <c r="G95">
         <v>9.640000000000001</v>
@@ -9062,37 +9062,37 @@
         <v>2.574</v>
       </c>
       <c r="M95">
-        <v>64.94204636828475</v>
+        <v>65.64034794213728</v>
       </c>
       <c r="N95">
-        <v>-62.36804636828475</v>
+        <v>-63.06634794213728</v>
       </c>
       <c r="O95">
-        <v>-16.09095596301747</v>
+        <v>-16.27111776907142</v>
       </c>
       <c r="P95">
-        <v>-46.27709040526729</v>
+        <v>-46.79523017306586</v>
       </c>
       <c r="Q95">
-        <v>-45.86509040526729</v>
+        <v>-46.38323017306586</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3686906518196513</v>
+        <v>0.42250576045626</v>
       </c>
       <c r="T95">
-        <v>7.457058933479245</v>
+        <v>8.699902089059123</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01022591736998786</v>
+        <v>0.01011713101498799</v>
       </c>
       <c r="W95">
-        <v>0.2333887286841569</v>
+        <v>0.2334143805066658</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.03963533864336377</v>
+        <v>0.03921368610460452</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9108,22 +9108,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2447598633036415</v>
+        <v>0.2466598633036415</v>
       </c>
       <c r="C96">
-        <v>-248.5336014373804</v>
+        <v>-251.6860886696976</v>
       </c>
       <c r="D96">
-        <v>20.19937541646723</v>
+        <v>20.00830283153136</v>
       </c>
       <c r="E96">
-        <v>-17.50548788428813</v>
+        <v>-14.5440732369068</v>
       </c>
       <c r="F96">
-        <v>278.3729768538477</v>
+        <v>281.334391501229</v>
       </c>
       <c r="G96">
         <v>9.640000000000001</v>
@@ -9144,37 +9144,37 @@
         <v>2.574</v>
       </c>
       <c r="M96">
-        <v>65.64034794213728</v>
+        <v>66.3386495159898</v>
       </c>
       <c r="N96">
-        <v>-63.06634794213728</v>
+        <v>-63.7646495159898</v>
       </c>
       <c r="O96">
-        <v>-16.27111776907142</v>
+        <v>-16.45127957512537</v>
       </c>
       <c r="P96">
-        <v>-46.79523017306586</v>
+        <v>-47.31336994086443</v>
       </c>
       <c r="Q96">
-        <v>-46.38323017306586</v>
+        <v>-46.90136994086443</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.42250576045626</v>
+        <v>0.4978469125475122</v>
       </c>
       <c r="T96">
-        <v>8.699902089059123</v>
+        <v>10.43988250687095</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01011713101498799</v>
+        <v>0.01001063489904075</v>
       </c>
       <c r="W96">
-        <v>0.2334143805066658</v>
+        <v>0.2334394922908062</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.03921368610460452</v>
+        <v>0.03880091046139822</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9190,22 +9190,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2466598633036415</v>
+        <v>0.2485598633036415</v>
       </c>
       <c r="C97">
-        <v>-251.6860886696976</v>
+        <v>-254.8349949377603</v>
       </c>
       <c r="D97">
-        <v>20.00830283153136</v>
+        <v>19.8208112108501</v>
       </c>
       <c r="E97">
-        <v>-14.5440732369068</v>
+        <v>-11.58265858952541</v>
       </c>
       <c r="F97">
-        <v>281.334391501229</v>
+        <v>284.2958061486104</v>
       </c>
       <c r="G97">
         <v>9.640000000000001</v>
@@ -9226,37 +9226,37 @@
         <v>2.574</v>
       </c>
       <c r="M97">
-        <v>66.3386495159898</v>
+        <v>67.03695108984233</v>
       </c>
       <c r="N97">
-        <v>-63.7646495159898</v>
+        <v>-64.46295108984233</v>
       </c>
       <c r="O97">
-        <v>-16.45127957512537</v>
+        <v>-16.63144138117932</v>
       </c>
       <c r="P97">
-        <v>-47.31336994086443</v>
+        <v>-47.83150970866301</v>
       </c>
       <c r="Q97">
-        <v>-46.90136994086443</v>
+        <v>-47.41950970866301</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4978469125475122</v>
+        <v>0.6108586406843904</v>
       </c>
       <c r="T97">
-        <v>10.43988250687095</v>
+        <v>13.0498531335887</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01001063489904075</v>
+        <v>0.009906357452175737</v>
       </c>
       <c r="W97">
-        <v>0.2334394922908062</v>
+        <v>0.233464080912777</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.03880091046139822</v>
+        <v>0.03839673431075863</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9272,22 +9272,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2485598633036415</v>
+        <v>0.2504598633036415</v>
       </c>
       <c r="C98">
-        <v>-254.8349949377602</v>
+        <v>-257.9804199753212</v>
       </c>
       <c r="D98">
-        <v>19.8208112108501</v>
+        <v>19.63680082067049</v>
       </c>
       <c r="E98">
-        <v>-11.58265858952547</v>
+        <v>-8.621243942144076</v>
       </c>
       <c r="F98">
-        <v>284.2958061486103</v>
+        <v>287.2572207959917</v>
       </c>
       <c r="G98">
         <v>9.640000000000001</v>
@@ -9308,37 +9308,37 @@
         <v>2.574</v>
       </c>
       <c r="M98">
-        <v>67.03695108984232</v>
+        <v>67.73525266369485</v>
       </c>
       <c r="N98">
-        <v>-64.46295108984232</v>
+        <v>-65.16125266369485</v>
       </c>
       <c r="O98">
-        <v>-16.63144138117932</v>
+        <v>-16.81160318723327</v>
       </c>
       <c r="P98">
-        <v>-47.83150970866301</v>
+        <v>-48.34964947646158</v>
       </c>
       <c r="Q98">
-        <v>-47.41950970866301</v>
+        <v>-47.93764947646158</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6108586406843889</v>
+        <v>0.7992115209125186</v>
       </c>
       <c r="T98">
-        <v>13.04985313358866</v>
+        <v>17.39980417811821</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.009906357452175739</v>
+        <v>0.009804230055761556</v>
       </c>
       <c r="W98">
-        <v>0.233464080912777</v>
+        <v>0.2334881625528514</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.03839673431075863</v>
+        <v>0.03800089168899823</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9354,22 +9354,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2504598633036415</v>
+        <v>0.2523598633036415</v>
       </c>
       <c r="C99">
-        <v>-257.9804199753212</v>
+        <v>-261.1224598466089</v>
       </c>
       <c r="D99">
-        <v>19.63680082067049</v>
+        <v>19.45617559676419</v>
       </c>
       <c r="E99">
-        <v>-8.621243942144076</v>
+        <v>-5.659829294762744</v>
       </c>
       <c r="F99">
-        <v>287.2572207959917</v>
+        <v>290.218635443373</v>
       </c>
       <c r="G99">
         <v>9.640000000000001</v>
@@ -9390,37 +9390,37 @@
         <v>2.574</v>
       </c>
       <c r="M99">
-        <v>67.73525266369485</v>
+        <v>68.43355423754737</v>
       </c>
       <c r="N99">
-        <v>-65.16125266369485</v>
+        <v>-65.85955423754737</v>
       </c>
       <c r="O99">
-        <v>-16.81160318723327</v>
+        <v>-16.99176499328722</v>
       </c>
       <c r="P99">
-        <v>-48.34964947646158</v>
+        <v>-48.86778924426015</v>
       </c>
       <c r="Q99">
-        <v>-47.93764947646158</v>
+        <v>-48.45578924426015</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7992115209125186</v>
+        <v>1.175917281368778</v>
       </c>
       <c r="T99">
-        <v>17.39980417811821</v>
+        <v>26.09970626717732</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.009804230055761556</v>
+        <v>0.009704186891927254</v>
       </c>
       <c r="W99">
-        <v>0.2334881625528514</v>
+        <v>0.2335117527308836</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.03800089168899823</v>
+        <v>0.03761312748809009</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9436,22 +9436,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2523598633036415</v>
+        <v>0.2542598633036415</v>
       </c>
       <c r="C100">
-        <v>-261.1224598466089</v>
+        <v>-264.2612071135555</v>
       </c>
       <c r="D100">
-        <v>19.45617559676419</v>
+        <v>19.27884297719891</v>
       </c>
       <c r="E100">
-        <v>-5.659829294762744</v>
+        <v>-2.698414647381355</v>
       </c>
       <c r="F100">
-        <v>290.218635443373</v>
+        <v>293.1800500907544</v>
       </c>
       <c r="G100">
         <v>9.640000000000001</v>
@@ -9472,37 +9472,37 @@
         <v>2.574</v>
       </c>
       <c r="M100">
-        <v>68.43355423754737</v>
+        <v>69.1318558113999</v>
       </c>
       <c r="N100">
-        <v>-65.85955423754737</v>
+        <v>-66.5578558113999</v>
       </c>
       <c r="O100">
-        <v>-16.99176499328722</v>
+        <v>-17.17192679934118</v>
       </c>
       <c r="P100">
-        <v>-48.86778924426015</v>
+        <v>-49.38592901205872</v>
       </c>
       <c r="Q100">
-        <v>-48.45578924426015</v>
+        <v>-48.97392901205873</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.175917281368778</v>
+        <v>2.306034562737556</v>
       </c>
       <c r="T100">
-        <v>26.09970626717732</v>
+        <v>52.19941253435464</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.009704186891927254</v>
+        <v>0.009606164802109806</v>
       </c>
       <c r="W100">
-        <v>0.2335117527308836</v>
+        <v>0.2335348663396625</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9510,91 +9510,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.03761312748809009</v>
+        <v>0.03723319690740234</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2542598633036415</v>
-      </c>
-      <c r="C101">
-        <v>-264.2612071135555</v>
-      </c>
-      <c r="D101">
-        <v>19.27884297719891</v>
-      </c>
-      <c r="E101">
-        <v>-2.698414647381355</v>
-      </c>
-      <c r="F101">
-        <v>293.1800500907544</v>
-      </c>
-      <c r="G101">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="H101">
-        <v>0.263</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.986</v>
-      </c>
-      <c r="K101">
-        <v>0.4119999999999999</v>
-      </c>
-      <c r="L101">
-        <v>2.574</v>
-      </c>
-      <c r="M101">
-        <v>69.1318558113999</v>
-      </c>
-      <c r="N101">
-        <v>-66.5578558113999</v>
-      </c>
-      <c r="O101">
-        <v>-17.17192679934118</v>
-      </c>
-      <c r="P101">
-        <v>-49.38592901205872</v>
-      </c>
-      <c r="Q101">
-        <v>-48.97392901205873</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.306034562737556</v>
-      </c>
-      <c r="T101">
-        <v>52.19941253435464</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.009606164802109806</v>
-      </c>
-      <c r="W101">
-        <v>0.2335348663396625</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.03723319690740234</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
